--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4191D6EB-6803-421F-AA68-53790911EB1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7088E4-11E3-4007-A1CA-84DB98ADDE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardInfo" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardInfo!$A$1:$J$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardInfo!$A$1:$I$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="142">
   <si>
     <t>CardId</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Price</t>
-  </si>
-  <si>
-    <t>UnlockLevel</t>
   </si>
   <si>
     <t>UpgradeId</t>
@@ -108,9 +105,6 @@
   <si>
     <t>价格
 用于商店消费</t>
-  </si>
-  <si>
-    <t>解锁等级</t>
   </si>
   <si>
     <t>升级后id</t>
@@ -1403,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -1414,11 +1408,10 @@
     <col min="6" max="6" width="69.6640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" style="4" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1443,335 +1436,326 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>12002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>12004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>12007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,19 +1763,19 @@
         <v>12012</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1799,19 +1783,19 @@
         <v>12013</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1819,19 +1803,19 @@
         <v>12014</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1839,19 +1823,19 @@
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1859,19 +1843,19 @@
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1879,19 +1863,19 @@
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1899,19 +1883,19 @@
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1919,19 +1903,19 @@
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1939,19 +1923,19 @@
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1959,19 +1943,19 @@
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1979,19 +1963,19 @@
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1999,19 +1983,19 @@
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2019,19 +2003,19 @@
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,19 +2023,19 @@
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2059,19 +2043,19 @@
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2079,19 +2063,19 @@
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,19 +2083,19 @@
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,19 +2103,19 @@
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>-1</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,19 +2123,19 @@
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2159,19 +2143,19 @@
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,19 +2163,19 @@
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2199,19 +2183,19 @@
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,19 +2203,19 @@
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2239,19 +2223,19 @@
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2259,19 +2243,19 @@
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2279,19 +2263,19 @@
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2299,19 +2283,19 @@
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2319,19 +2303,19 @@
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2339,19 +2323,19 @@
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2359,19 +2343,19 @@
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2379,19 +2363,19 @@
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2399,19 +2383,19 @@
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,19 +2403,19 @@
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2439,19 +2423,19 @@
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,19 +2443,19 @@
         <v>12046</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,19 +2463,19 @@
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E52" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,19 +2483,19 @@
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2519,19 +2503,19 @@
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2539,19 +2523,19 @@
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2559,19 +2543,19 @@
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2579,19 +2563,19 @@
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2599,19 +2583,19 @@
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2619,19 +2603,19 @@
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E59" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2639,19 +2623,19 @@
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2659,23 +2643,23 @@
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7088E4-11E3-4007-A1CA-84DB98ADDE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84453C4F-8EA8-4ED7-9426-BC3DB51D7699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>罕见</t>
   </si>
   <si>
-    <t>随机【御剑】，抽1张牌</t>
-  </si>
-  <si>
     <t>惊鸿</t>
   </si>
   <si>
@@ -303,720 +300,707 @@
     <t>剑来</t>
   </si>
   <si>
-    <t>【剑来】，抽1张牌</t>
-  </si>
-  <si>
     <t>并锋</t>
   </si>
   <si>
     <t>乾坤</t>
   </si>
   <si>
+    <t>步月</t>
+  </si>
+  <si>
+    <t>回风</t>
+  </si>
+  <si>
+    <t>【剑来】。获得6点【护甲】</t>
+  </si>
+  <si>
+    <t>远遁</t>
+  </si>
+  <si>
+    <t>【遁形】到随机位置，获得10点【护甲】</t>
+  </si>
+  <si>
+    <t>游龙</t>
+  </si>
+  <si>
+    <t>【飞剑】造成7点途经伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>遁影</t>
+  </si>
+  <si>
+    <t>【遁形】1距离，如果【易位】则【剑来】</t>
+  </si>
+  <si>
+    <t>寒芒</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【剑来】。抽1张牌，如果</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【灵剑】获得1点能量</t>
+    </r>
+  </si>
+  <si>
+    <t>追魂</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【剑来】。如果</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【灵剑】，抽1张牌</t>
+    </r>
+  </si>
+  <si>
+    <t>聚灵</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【剑来】。每</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1道【灵剑】获得1能量并抽1张牌</t>
+    </r>
+  </si>
+  <si>
+    <t>御灵</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着，在指定位置生成【灵剑】。【剑来】</t>
+  </si>
+  <si>
+    <t>灵遁</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【遁形】1距离。如果移动到【灵剑】位置</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【灵剑】，获得12【护甲】</t>
+    </r>
+  </si>
+  <si>
+    <t>剑翼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【遁形】到【飞剑】/【灵剑】。如果到【飞剑】位置获得9【护甲】；如果到【灵剑】位置，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>并获得18【护甲】</t>
+    </r>
+  </si>
+  <si>
+    <t>天罡</t>
+  </si>
+  <si>
+    <t>如果处于停止则【旋剑】，抽1张牌；如果处于【旋剑】则停止且获得3点能量</t>
+  </si>
+  <si>
+    <t>藏锋</t>
+  </si>
+  <si>
+    <t>重铸</t>
+  </si>
+  <si>
+    <t>崩锋</t>
+  </si>
+  <si>
+    <t>【旋剑】。抽1张牌，弃掉1张手牌</t>
+  </si>
+  <si>
+    <t>御风</t>
+  </si>
+  <si>
+    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
+  </si>
+  <si>
+    <t>化莲</t>
+  </si>
+  <si>
+    <t>【剑来】。对途经敌人造成1次完整【旋剑】伤害随后停止</t>
+  </si>
+  <si>
+    <t>断江</t>
+  </si>
+  <si>
+    <t>横舟</t>
+  </si>
+  <si>
+    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
+  </si>
+  <si>
+    <t>赶月</t>
+  </si>
+  <si>
+    <t>【御剑】且不停止【旋剑】状态</t>
+  </si>
+  <si>
+    <t>流光</t>
+  </si>
+  <si>
+    <t>刹那</t>
+  </si>
+  <si>
+    <t>天华</t>
+  </si>
+  <si>
+    <t>【旋剑】4次</t>
+  </si>
+  <si>
+    <t>铸芒</t>
+  </si>
+  <si>
+    <t>造成4点伤害。【旋剑】</t>
+  </si>
+  <si>
+    <t>碎星</t>
+  </si>
+  <si>
+    <t>白虹</t>
+  </si>
+  <si>
+    <t>星河</t>
+  </si>
+  <si>
+    <t>【旋剑】会对【灵剑】一起生效。【消耗】</t>
+  </si>
+  <si>
+    <t>蚀髓</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着【灵剑】，恢复7点生命值</t>
+  </si>
+  <si>
+    <t>碧海潮生</t>
+  </si>
+  <si>
+    <t>每摧毁2把【灵剑】就随机在空位置生成一道【灵剑】。【消耗】</t>
+  </si>
+  <si>
+    <t>种灵</t>
+  </si>
+  <si>
+    <t>随机在3处空位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>灵附</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着剑灵，在指定位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>灵潮</t>
+  </si>
+  <si>
+    <t>每回合开始随机位置生成一道【灵剑】。【灵剑】途经造成9点伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>归尘</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>摧毁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>指定位置的【灵剑】，恢复能量至上限</t>
+    </r>
+  </si>
+  <si>
+    <t>牵络</t>
+  </si>
+  <si>
+    <t>【链接】。本次【链接】施加12点【护甲】</t>
+  </si>
+  <si>
+    <t>贯脉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则再次【链接】</t>
+    </r>
+  </si>
+  <si>
+    <t>缠丝</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。对【链接】的敌人施加2层【虚弱】，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则再施加1层【易伤】</t>
+    </r>
+  </si>
+  <si>
+    <t>分野</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则获得1点能量</t>
+    </r>
+  </si>
+  <si>
+    <t>扫弦</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。对【链接】的敌人施加2层【易伤】，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则抽2张牌</t>
+    </r>
+  </si>
+  <si>
+    <t>天罗</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。消耗所有【护甲】，对全体敌人造成等量伤害。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则恢复一半【护甲】</t>
+    </r>
+  </si>
+  <si>
+    <t>北斗</t>
+  </si>
+  <si>
+    <t>【链接】均视为穿透所有敌人。【消耗】</t>
+  </si>
+  <si>
+    <t>空弦</t>
+  </si>
+  <si>
+    <t>【链接】。不获得【护甲】，每【链接】1名敌人获得1点能量</t>
+  </si>
+  <si>
+    <t>初照</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【链接】。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穿透</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有敌人则全体造成4点伤害</t>
+    </r>
+  </si>
+  <si>
+    <t>离身</t>
+  </si>
+  <si>
+    <t>【链接】。随机去除1个负面效果</t>
+  </si>
+  <si>
+    <t>连丝</t>
+  </si>
+  <si>
+    <t>【链接】。抽1张牌，弃1张手牌</t>
+  </si>
+  <si>
+    <t>凝雪</t>
+  </si>
+  <si>
+    <t>【御剑】。【链接】。抽1张牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【旋剑】。对剑格敌人造成5*(X+1)点伤害</t>
+  </si>
+  <si>
+    <t>立即对剑格以及邻格敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>【御剑】。如果是邻格则造成9点途经伤害</t>
+  </si>
+  <si>
+    <t>【旋剑】对邻格也造成伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>【御剑】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成6点伤害，【御剑】至该格但不造成途经伤害。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【旋剑】。人剑合一获得1点能量</t>
+  </si>
+  <si>
+    <t>【旋剑】2次。人剑合一则随机对1名敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>获得1点能量，人剑合一再获得1点能量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【剑来】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【御剑】到随机位置，抽1张牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有正在【旋剑】的【飞剑】和【灵剑】伤害翻倍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【链接】。对所有【链接】【灵剑】的位置造成6点伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>【遁形】1距离。如果与敌人【易位】，获得7点【护甲】</t>
-  </si>
-  <si>
-    <t>步月</t>
-  </si>
-  <si>
-    <r>
-      <t>【遁形】</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>距离。获得5点【护甲】</t>
-    </r>
-  </si>
-  <si>
-    <t>回风</t>
-  </si>
-  <si>
-    <t>【剑来】。获得6点【护甲】</t>
-  </si>
-  <si>
-    <t>远遁</t>
-  </si>
-  <si>
-    <t>【遁形】到随机位置，获得10点【护甲】</t>
-  </si>
-  <si>
-    <t>游龙</t>
-  </si>
-  <si>
-    <t>【飞剑】造成7点途经伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>遁影</t>
-  </si>
-  <si>
-    <t>【遁形】1距离，如果【易位】则【剑来】</t>
-  </si>
-  <si>
-    <t>寒芒</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【剑来】。抽1张牌，如果</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【灵剑】获得1点能量</t>
-    </r>
-  </si>
-  <si>
-    <t>追魂</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【剑来】。如果</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【灵剑】，抽1张牌</t>
-    </r>
-  </si>
-  <si>
-    <t>聚灵</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【剑来】。每</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1道【灵剑】获得1能量并抽1张牌</t>
-    </r>
-  </si>
-  <si>
-    <t>御灵</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着，在指定位置生成【灵剑】。【剑来】</t>
-  </si>
-  <si>
-    <t>灵遁</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【遁形】1距离。如果移动到【灵剑】位置</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【灵剑】，获得12【护甲】</t>
-    </r>
-  </si>
-  <si>
-    <t>剑翼</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【遁形】到【飞剑】/【灵剑】。如果到【飞剑】位置获得9【护甲】；如果到【灵剑】位置，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>并获得18【护甲】</t>
-    </r>
-  </si>
-  <si>
-    <t>天罡</t>
-  </si>
-  <si>
-    <t>如果处于停止则【旋剑】，抽1张牌；如果处于【旋剑】则停止且获得3点能量</t>
-  </si>
-  <si>
-    <t>藏锋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【遁形】2距离。获得5点【护甲】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>手牌内所有含有【旋剑】的牌费用减1</t>
-  </si>
-  <si>
-    <t>重铸</t>
-  </si>
-  <si>
-    <t>崩锋</t>
-  </si>
-  <si>
-    <t>【旋剑】。抽1张牌，弃掉1张手牌</t>
-  </si>
-  <si>
-    <t>御风</t>
-  </si>
-  <si>
-    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
-  </si>
-  <si>
-    <t>化莲</t>
-  </si>
-  <si>
-    <t>【剑来】。对途经敌人造成1次完整【旋剑】伤害随后停止</t>
-  </si>
-  <si>
-    <t>断江</t>
-  </si>
-  <si>
-    <t>横舟</t>
-  </si>
-  <si>
-    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
-  </si>
-  <si>
-    <t>赶月</t>
-  </si>
-  <si>
-    <t>【御剑】且不停止【旋剑】状态</t>
-  </si>
-  <si>
-    <t>流光</t>
-  </si>
-  <si>
-    <t>刹那</t>
-  </si>
-  <si>
-    <t>所有位置【旋剑】伤害翻倍</t>
-  </si>
-  <si>
-    <t>天华</t>
-  </si>
-  <si>
-    <t>【旋剑】4次</t>
-  </si>
-  <si>
-    <t>铸芒</t>
-  </si>
-  <si>
-    <t>造成4点伤害。【旋剑】</t>
-  </si>
-  <si>
-    <t>碎星</t>
-  </si>
-  <si>
-    <t>白虹</t>
-  </si>
-  <si>
-    <t>星河</t>
-  </si>
-  <si>
-    <t>【旋剑】会对【灵剑】一起生效。【消耗】</t>
-  </si>
-  <si>
-    <t>蚀髓</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着【灵剑】，恢复7点生命值</t>
-  </si>
-  <si>
-    <t>碧海潮生</t>
-  </si>
-  <si>
-    <t>每摧毁2把【灵剑】就随机在空位置生成一道【灵剑】。【消耗】</t>
-  </si>
-  <si>
-    <t>种灵</t>
-  </si>
-  <si>
-    <t>随机在3处空位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>灵附</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着剑灵，在指定位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>灵潮</t>
-  </si>
-  <si>
-    <t>每回合开始随机位置生成一道【灵剑】。【灵剑】途经造成9点伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>归尘</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>摧毁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>指定位置的【灵剑】，恢复能量至上限</t>
-    </r>
-  </si>
-  <si>
-    <t>牵络</t>
-  </si>
-  <si>
-    <t>【链接】。本次【链接】施加12点【护甲】</t>
-  </si>
-  <si>
-    <t>贯脉</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则再次【链接】</t>
-    </r>
-  </si>
-  <si>
-    <t>缠丝</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。对【链接】的敌人施加2层【虚弱】，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则再施加1层【易伤】</t>
-    </r>
-  </si>
-  <si>
-    <t>分野</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则获得1点能量</t>
-    </r>
-  </si>
-  <si>
-    <t>扫弦</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。对【链接】的敌人施加2层【易伤】，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则抽2张牌</t>
-    </r>
-  </si>
-  <si>
-    <t>天罗</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。消耗所有【护甲】，对全体敌人造成等量伤害。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则恢复一半【护甲】</t>
-    </r>
-  </si>
-  <si>
-    <t>北斗</t>
-  </si>
-  <si>
-    <t>【链接】均视为穿透所有敌人。【消耗】</t>
-  </si>
-  <si>
-    <t>空弦</t>
-  </si>
-  <si>
-    <t>【链接】。不获得【护甲】，每【链接】1名敌人获得1点能量</t>
-  </si>
-  <si>
-    <t>初照</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>【链接】。</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>穿透</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有敌人则全体造成4点伤害</t>
-    </r>
-  </si>
-  <si>
-    <t>离身</t>
-  </si>
-  <si>
-    <t>【链接】。随机去除1个负面效果</t>
-  </si>
-  <si>
-    <t>连丝</t>
-  </si>
-  <si>
-    <t>【链接】。抽1张牌，弃1张手牌</t>
-  </si>
-  <si>
-    <t>凝雪</t>
-  </si>
-  <si>
-    <t>【链接】。对所有【链接】【灵剑】的位置造成6点伤害</t>
-  </si>
-  <si>
-    <t>【御剑】。【链接】。抽1张牌</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>【旋剑】。对剑格敌人造成5*(X+1)点伤害</t>
-  </si>
-  <si>
-    <t>立即对剑格以及邻格敌人造成【旋剑】伤害</t>
-  </si>
-  <si>
-    <t>【御剑】。如果是邻格则造成9点途经伤害</t>
-  </si>
-  <si>
-    <t>【旋剑】对邻格也造成伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>【御剑】</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成6点伤害，【御剑】至该格但不造成途经伤害。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得1点能量，人剑合一再获得1点能量</t>
-  </si>
-  <si>
-    <t>【旋剑】。人剑合一获得1点能量</t>
-  </si>
-  <si>
-    <t>【旋剑】2次。人剑合一则随机对1名敌人造成【旋剑】伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1032,24 +1016,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1071,18 +1040,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1097,7 +1060,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1115,11 +1078,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1514,8 +1476,8 @@
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>138</v>
+      <c r="F4" s="8" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1534,8 +1496,8 @@
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>137</v>
+      <c r="F5" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1554,8 +1516,8 @@
       <c r="E6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
+      <c r="F6" s="8" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,7 +1525,7 @@
         <v>12003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1575,7 +1537,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1583,7 +1545,7 @@
         <v>12004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1595,7 +1557,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1603,7 +1565,7 @@
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1614,8 +1576,8 @@
       <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>132</v>
+      <c r="F9" s="8" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1623,7 +1585,7 @@
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1632,10 +1594,10 @@
         <v>21</v>
       </c>
       <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1643,19 +1605,19 @@
         <v>12007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1663,7 +1625,7 @@
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1675,7 +1637,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1683,19 +1645,19 @@
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,19 +1665,19 @@
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>43</v>
+      <c r="F14" s="8" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1723,19 +1685,19 @@
         <v>12010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>139</v>
+      <c r="F15" s="8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,19 +1705,19 @@
         <v>12011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="7">
+        <v>43</v>
+      </c>
+      <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>46</v>
+      <c r="F16" s="8" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1763,19 +1725,19 @@
         <v>12012</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>48</v>
+      <c r="F17" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,19 +1745,19 @@
         <v>12013</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,19 +1765,19 @@
         <v>12014</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,19 +1785,19 @@
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,19 +1805,19 @@
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,19 +1825,19 @@
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,19 +1845,19 @@
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1903,19 +1865,19 @@
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,19 +1885,19 @@
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,19 +1905,19 @@
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1963,19 +1925,19 @@
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1983,19 +1945,19 @@
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>70</v>
+      <c r="F28" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2003,19 +1965,19 @@
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
+        <v>68</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2023,9 +1985,9 @@
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="2">
+        <v>69</v>
+      </c>
+      <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
@@ -2035,7 +1997,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>140</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2043,19 +2005,19 @@
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2063,19 +2025,19 @@
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
         <v>25</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2083,19 +2045,19 @@
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2103,10 +2065,10 @@
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
@@ -2115,7 +2077,7 @@
         <v>25</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,7 +2085,7 @@
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2132,10 +2094,10 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2143,19 +2105,19 @@
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>84</v>
+        <v>31</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2163,19 +2125,19 @@
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>136</v>
+        <v>25</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2183,19 +2145,19 @@
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2203,10 +2165,10 @@
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
@@ -2215,7 +2177,7 @@
         <v>22</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2223,19 +2185,19 @@
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2243,19 +2205,19 @@
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>134</v>
+        <v>22</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2263,19 +2225,19 @@
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>141</v>
+        <v>31</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2283,19 +2245,19 @@
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2303,19 +2265,19 @@
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E44" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2323,19 +2285,19 @@
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2343,19 +2305,19 @@
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,19 +2325,19 @@
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E47" t="s">
         <v>22</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,19 +2345,19 @@
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,19 +2365,19 @@
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E49" t="s">
         <v>25</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>107</v>
+      <c r="F49" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,19 +2385,19 @@
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E50" t="s">
         <v>22</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,19 +2405,19 @@
         <v>12046</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E51" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,19 +2425,19 @@
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E52" t="s">
         <v>25</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,19 +2445,19 @@
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" t="s">
         <v>22</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,19 +2465,19 @@
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E54" t="s">
         <v>25</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,19 +2485,19 @@
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2543,19 +2505,19 @@
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E56" t="s">
         <v>25</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,19 +2525,19 @@
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57" t="s">
         <v>22</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,19 +2545,19 @@
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E58" t="s">
         <v>22</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,19 +2565,19 @@
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" t="s">
         <v>25</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,19 +2585,19 @@
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E60" t="s">
         <v>22</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,24 +2605,24 @@
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E61" t="s">
         <v>22</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>131</v>
+      <c r="F61" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBBCFC6-FB5C-4E13-8787-1FF7863746F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048A2E17-0189-4A30-91EC-AD4E51A9B2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,25 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardInfo!$A$1:$I$61</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="253">
   <si>
     <t>CardId</t>
   </si>
@@ -63,6 +50,102 @@
   </si>
   <si>
     <t>UpgradeId</t>
+  </si>
+  <si>
+    <t>SlotAction</t>
+  </si>
+  <si>
+    <t>SlotDistance</t>
+  </si>
+  <si>
+    <t>Effect1_Type</t>
+  </si>
+  <si>
+    <t>Effect1_Target</t>
+  </si>
+  <si>
+    <t>Effect1_Param1</t>
+  </si>
+  <si>
+    <t>Effect1_Param2</t>
+  </si>
+  <si>
+    <t>Effect1_Condition</t>
+  </si>
+  <si>
+    <t>Effect2_Type</t>
+  </si>
+  <si>
+    <t>Effect2_Target</t>
+  </si>
+  <si>
+    <t>Effect2_Param1</t>
+  </si>
+  <si>
+    <t>Effect2_Param2</t>
+  </si>
+  <si>
+    <t>Effect2_Condition</t>
+  </si>
+  <si>
+    <t>Effect3_Type</t>
+  </si>
+  <si>
+    <t>Effect3_Target</t>
+  </si>
+  <si>
+    <t>Effect3_Param1</t>
+  </si>
+  <si>
+    <t>Effect3_Param2</t>
+  </si>
+  <si>
+    <t>Effect3_Condition</t>
+  </si>
+  <si>
+    <t>Effect4_Type</t>
+  </si>
+  <si>
+    <t>Effect4_Target</t>
+  </si>
+  <si>
+    <t>Effect4_Param1</t>
+  </si>
+  <si>
+    <t>Effect4_Param2</t>
+  </si>
+  <si>
+    <t>Effect4_Condition</t>
+  </si>
+  <si>
+    <t>Effect5_Type</t>
+  </si>
+  <si>
+    <t>Effect5_Target</t>
+  </si>
+  <si>
+    <t>Effect5_Param1</t>
+  </si>
+  <si>
+    <t>Effect5_Param2</t>
+  </si>
+  <si>
+    <t>Effect5_Condition</t>
+  </si>
+  <si>
+    <t>Effect6_Type</t>
+  </si>
+  <si>
+    <t>Effect6_Target</t>
+  </si>
+  <si>
+    <t>Effect6_Param1</t>
+  </si>
+  <si>
+    <t>Effect6_Param2</t>
+  </si>
+  <si>
+    <t>Effect6_Condition</t>
   </si>
   <si>
     <t>int</t>
@@ -94,392 +177,624 @@
 史诗</t>
   </si>
   <si>
-    <t>美术资源加载地址</t>
-  </si>
-  <si>
-    <t>价格
-用于商店消费</t>
-  </si>
-  <si>
-    <t>升级后id</t>
-  </si>
-  <si>
-    <t>刺</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>醉剑</t>
-  </si>
-  <si>
-    <t>罕见</t>
-  </si>
-  <si>
-    <t>惊鸿</t>
-  </si>
-  <si>
-    <t>穿云</t>
-  </si>
-  <si>
-    <t>剑罡</t>
-  </si>
-  <si>
-    <t>逐星</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>万剑诀</t>
-  </si>
-  <si>
-    <t>能力</t>
-  </si>
-  <si>
-    <t>连环</t>
-  </si>
-  <si>
-    <t>护体</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>并锋</t>
-  </si>
-  <si>
-    <t>乾坤</t>
-  </si>
-  <si>
-    <t>步月</t>
-  </si>
-  <si>
-    <t>回风</t>
-  </si>
-  <si>
-    <t>远遁</t>
-  </si>
-  <si>
-    <t>游龙</t>
-  </si>
-  <si>
-    <t>遁影</t>
-  </si>
-  <si>
-    <t>寒芒</t>
-  </si>
-  <si>
-    <t>追魂</t>
-  </si>
-  <si>
-    <t>聚灵</t>
-  </si>
-  <si>
-    <t>御灵</t>
-  </si>
-  <si>
-    <t>灵遁</t>
-  </si>
-  <si>
-    <t>剑翼</t>
-  </si>
-  <si>
-    <t>天罡</t>
-  </si>
-  <si>
-    <t>藏锋</t>
-  </si>
-  <si>
-    <t>重铸</t>
-  </si>
-  <si>
-    <t>崩锋</t>
-  </si>
-  <si>
-    <t>御风</t>
-  </si>
-  <si>
-    <t>化莲</t>
-  </si>
-  <si>
-    <t>断江</t>
-  </si>
-  <si>
-    <t>横舟</t>
-  </si>
-  <si>
-    <t>赶月</t>
-  </si>
-  <si>
-    <t>流光</t>
-  </si>
-  <si>
-    <t>刹那</t>
-  </si>
-  <si>
-    <t>天华</t>
-  </si>
-  <si>
-    <t>铸芒</t>
-  </si>
-  <si>
-    <t>碎星</t>
-  </si>
-  <si>
-    <t>白虹</t>
-  </si>
-  <si>
-    <t>星河</t>
-  </si>
-  <si>
-    <t>蚀髓</t>
-  </si>
-  <si>
-    <t>碧海潮生</t>
-  </si>
-  <si>
-    <t>种灵</t>
-  </si>
-  <si>
-    <t>灵附</t>
-  </si>
-  <si>
-    <t>灵潮</t>
-  </si>
-  <si>
-    <t>归尘</t>
-  </si>
-  <si>
-    <t>牵络</t>
-  </si>
-  <si>
-    <t>贯脉</t>
-  </si>
-  <si>
-    <t>缠丝</t>
-  </si>
-  <si>
-    <t>分野</t>
-  </si>
-  <si>
-    <t>扫弦</t>
-  </si>
-  <si>
-    <t>天罗</t>
-  </si>
-  <si>
-    <t>北斗</t>
-  </si>
-  <si>
-    <t>空弦</t>
-  </si>
-  <si>
-    <t>初照</t>
-  </si>
-  <si>
-    <t>离身</t>
-  </si>
-  <si>
-    <t>连丝</t>
-  </si>
-  <si>
-    <t>凝雪</t>
-  </si>
-  <si>
-    <t>获得1点能量，人剑合一再获得1点能量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>描述文本
 可在此处修改参数然后重新生成，但是改描述需要动代码
 词条标记词条名称
 词条表已注册名称的词条关联文本会自动查询并展示</t>
   </si>
   <si>
+    <t>美术资源加载地址</t>
+  </si>
+  <si>
+    <t>价格
+用于商店消费</t>
+  </si>
+  <si>
+    <t>升级后id</t>
+  </si>
+  <si>
+    <t>刺</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>造成6点伤害，【御剑】至该格但不造成途经伤害。</t>
+  </si>
+  <si>
+    <t>bear</t>
+  </si>
+  <si>
+    <t>MoveSword</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DealDamage</t>
+  </si>
+  <si>
+    <t>ManualEnemy</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>SetSwordFlag</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>SuppressPathDamage</t>
+  </si>
+  <si>
+    <t>御剑</t>
+  </si>
+  <si>
+    <t>【御剑】</t>
+  </si>
+  <si>
+    <t>醉剑</t>
+  </si>
+  <si>
+    <t>罕见</t>
+  </si>
+  <si>
+    <t>【御剑】到随机位置，抽1张牌</t>
+  </si>
+  <si>
+    <t>DrawCards</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RideSword</t>
+  </si>
+  <si>
+    <t>惊鸿</t>
+  </si>
+  <si>
+    <t>【御剑】。如果【御剑】到邻格则造成9点途经伤害</t>
+  </si>
+  <si>
+    <t>PathDamageIfAdjacent</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>穿云</t>
+  </si>
+  <si>
+    <t>【御剑】并对目标位置造成6点伤害，之后【链接】。穿透所有敌人则获得1点能量</t>
+  </si>
+  <si>
+    <t>LinkSwords</t>
+  </si>
+  <si>
+    <t>GainEnergy</t>
+  </si>
+  <si>
+    <t>Penetrated</t>
+  </si>
+  <si>
+    <t>剑罡</t>
+  </si>
+  <si>
+    <t>【御剑】。【链接】。抽1张牌</t>
+  </si>
+  <si>
+    <t>逐星</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>SlotHasSpiritSword</t>
+  </si>
+  <si>
+    <t>ReturnToHand</t>
+  </si>
+  <si>
+    <t>DestroySpirit</t>
+  </si>
+  <si>
+    <t>万剑诀</t>
+  </si>
+  <si>
+    <t>能力</t>
+  </si>
+  <si>
+    <t>【御剑】控制所有【灵剑】至目标之后摧毁，每一道【灵剑】对目标造成11点伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>RecallSpiritsOnSwordMove</t>
+  </si>
+  <si>
+    <t>Exhaust</t>
+  </si>
+  <si>
+    <t>连环</t>
+  </si>
+  <si>
+    <t>【御剑】。对目标位置造成8点伤害。如果存在【灵剑】，摧毁并造成18点伤害</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>护体</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>【遁形】1距离，获得7点【护甲】</t>
+  </si>
+  <si>
+    <t>MovePlayer</t>
+  </si>
+  <si>
+    <t>GainBlock</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>剑来</t>
+  </si>
+  <si>
+    <t>【剑来】</t>
+  </si>
+  <si>
+    <t>RecallSwords</t>
+  </si>
+  <si>
+    <t>并锋</t>
+  </si>
+  <si>
+    <t>获得1点能量，人剑合一再获得1点能量</t>
+  </si>
+  <si>
+    <t>ManSwordUnity</t>
+  </si>
+  <si>
+    <t>乾坤</t>
+  </si>
+  <si>
+    <t>【遁形】1距离。如果与敌人【易位】，获得7点【护甲】</t>
+  </si>
+  <si>
+    <t>SlotHasEnemy</t>
+  </si>
+  <si>
+    <t>步月</t>
+  </si>
+  <si>
+    <t>【遁形】2距离。获得5点【护甲】</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>回风</t>
+  </si>
+  <si>
+    <t>【剑来】。获得6点【护甲】</t>
+  </si>
+  <si>
+    <t>远遁</t>
+  </si>
+  <si>
+    <t>【遁形】到随机位置，获得10点【护甲】</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>MovePlayerRandom</t>
+  </si>
+  <si>
+    <t>游龙</t>
+  </si>
+  <si>
     <t>【飞剑】造成7点途经伤害。【消耗】</t>
   </si>
   <si>
-    <t>造成6点伤害，【御剑】至该格但不造成途经伤害。</t>
-  </si>
-  <si>
-    <t>【御剑】</t>
-  </si>
-  <si>
-    <t>【御剑】到随机位置，抽1张牌</t>
-  </si>
-  <si>
-    <t>【御剑】。如果【御剑】到邻格则造成9点途经伤害</t>
-  </si>
-  <si>
-    <t>【遁形】1距离，获得7点【护甲】</t>
-  </si>
-  <si>
-    <t>【遁形】2距离。获得5点【护甲】</t>
-  </si>
-  <si>
-    <t>【遁形】到随机位置，获得10点【护甲】</t>
-  </si>
-  <si>
-    <t>【遁形】1距离。如果与敌人【易位】，获得7点【护甲】</t>
-  </si>
-  <si>
-    <t>【剑来】</t>
-  </si>
-  <si>
-    <t>【剑来】。获得6点【护甲】</t>
+    <t>SetCustomPathDamage</t>
+  </si>
+  <si>
+    <t>遁影</t>
   </si>
   <si>
     <t>【遁形】1距离，如果【易位】则【剑来】</t>
   </si>
   <si>
-    <t>【御剑】并对目标位置造成6点伤害，之后【链接】。穿透所有敌人则获得1点能量</t>
-  </si>
-  <si>
-    <t>【御剑】。【链接】。抽1张牌</t>
+    <t>RecallToSlot</t>
+  </si>
+  <si>
+    <t>MovePlayerToSlot</t>
+  </si>
+  <si>
+    <t>寒芒</t>
+  </si>
+  <si>
+    <t>【剑来】。抽1张牌，如果摧毁任何【灵剑】获得1点能量</t>
+  </si>
+  <si>
+    <t>HasSpiritSword</t>
+  </si>
+  <si>
+    <t>追魂</t>
+  </si>
+  <si>
+    <t>【剑来】。如果摧毁【灵剑】，抽1张牌</t>
+  </si>
+  <si>
+    <t>聚灵</t>
+  </si>
+  <si>
+    <t>【剑来】。每摧毁1道【灵剑】获得1能量并抽1张牌</t>
+  </si>
+  <si>
+    <t>PerSpiritEnergy</t>
+  </si>
+  <si>
+    <t>PerSpiritDraw</t>
+  </si>
+  <si>
+    <t>灵遁</t>
+  </si>
+  <si>
+    <t>【遁形】1距离。如果移动到【灵剑】位置摧毁【灵剑】，获得12【护甲】</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>剑翼</t>
+  </si>
+  <si>
+    <t>【遁形】到【飞剑】/【灵剑】。如果到【飞剑】位置获得9【护甲】；如果到【灵剑】位置，摧毁并获得18【护甲】</t>
+  </si>
+  <si>
+    <t>SlotHasSword</t>
+  </si>
+  <si>
+    <t>天罡</t>
+  </si>
+  <si>
+    <t>如果处于停止则【旋剑】，抽1张牌；如果处于【旋剑】则停止且获得3点能量</t>
+  </si>
+  <si>
+    <t>TianGang</t>
+  </si>
+  <si>
+    <t>藏锋</t>
+  </si>
+  <si>
+    <t>手牌内所有含有【旋剑】的牌费用减1</t>
+  </si>
+  <si>
+    <t>ReduceSpinCost</t>
+  </si>
+  <si>
+    <t>重铸</t>
+  </si>
+  <si>
+    <t>【旋剑】。人剑合一获得1点能量</t>
+  </si>
+  <si>
+    <t>SpinSword</t>
+  </si>
+  <si>
+    <t>崩锋</t>
+  </si>
+  <si>
+    <t>【旋剑】。抽1张牌，弃掉1张手牌</t>
+  </si>
+  <si>
+    <t>InteractiveDiscard</t>
+  </si>
+  <si>
+    <t>御风</t>
+  </si>
+  <si>
+    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
+  </si>
+  <si>
+    <t>GainSpinBlock</t>
+  </si>
+  <si>
+    <t>化莲</t>
+  </si>
+  <si>
+    <t>【剑来】。对途经敌人造成1次完整【旋剑】伤害随后停止</t>
+  </si>
+  <si>
+    <t>RecallSpinDamage</t>
+  </si>
+  <si>
+    <t>StopSpin</t>
+  </si>
+  <si>
+    <t>断江</t>
+  </si>
+  <si>
+    <t>【旋剑】。对剑格敌人造成5*(X+1)点伤害</t>
+  </si>
+  <si>
+    <t>SpinFormulaDamage</t>
+  </si>
+  <si>
+    <t>横舟</t>
+  </si>
+  <si>
+    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
+  </si>
+  <si>
+    <t>SpinDamageImmediate</t>
+  </si>
+  <si>
+    <t>赶月</t>
+  </si>
+  <si>
+    <t>【御剑】且不停止【旋剑】状态</t>
+  </si>
+  <si>
+    <t>KeepSpinningOnMove</t>
+  </si>
+  <si>
+    <t>流光</t>
+  </si>
+  <si>
+    <t>【旋剑】对邻格也造成伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>SpinHitsAdjacent</t>
+  </si>
+  <si>
+    <t>刹那</t>
+  </si>
+  <si>
+    <t>所有正在【旋剑】的【飞剑】和【灵剑】伤害翻倍</t>
+  </si>
+  <si>
+    <t>DoubleSpinDamage</t>
+  </si>
+  <si>
+    <t>天华</t>
+  </si>
+  <si>
+    <t>【旋剑】4次</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>铸芒</t>
+  </si>
+  <si>
+    <t>造成4点伤害。【旋剑】</t>
+  </si>
+  <si>
+    <t>碎星</t>
+  </si>
+  <si>
+    <t>立即对剑格以及邻格敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>白虹</t>
+  </si>
+  <si>
+    <t>【旋剑】2次。人剑合一则随机对1名敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>SpinDamageRandomEnemy</t>
+  </si>
+  <si>
+    <t>星河</t>
+  </si>
+  <si>
+    <t>【旋剑】会对【灵剑】一起生效。【消耗】</t>
+  </si>
+  <si>
+    <t>SpinAffectsSpirits</t>
+  </si>
+  <si>
+    <t>蚀髓</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着【灵剑】，恢复7点生命值</t>
+  </si>
+  <si>
+    <t>IsSpiritAttached</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>SpiritAttached</t>
+  </si>
+  <si>
+    <t>碧海潮生</t>
+  </si>
+  <si>
+    <t>每摧毁1把【灵剑】就随机在空位置生成一道【灵剑】。【消耗】</t>
+  </si>
+  <si>
+    <t>HasReactiveSpiritSpawn</t>
+  </si>
+  <si>
+    <t>种灵</t>
+  </si>
+  <si>
+    <t>随机在3处空位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>SpawnSpiritsRandom</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>御灵</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着，在指定位置生成【灵剑】。【剑来】</t>
+  </si>
+  <si>
+    <t>SpawnSpiritAtSlot</t>
+  </si>
+  <si>
+    <t>灵附</t>
+  </si>
+  <si>
+    <t>【附着·灵】。如果已经附着剑灵，在指定位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>灵潮</t>
+  </si>
+  <si>
+    <t>每回合开始随机位置生成一道【灵剑】。【灵剑】途经造成9点伤害。【消耗】</t>
+  </si>
+  <si>
+    <t>HasTurnStartSpiritSpawn</t>
+  </si>
+  <si>
+    <t>归尘</t>
+  </si>
+  <si>
+    <t>摧毁指定位置的【灵剑】，获得等同于上限的能量值</t>
+  </si>
+  <si>
+    <t>GainMaxEnergy</t>
+  </si>
+  <si>
+    <t>牵络</t>
   </si>
   <si>
     <t>【链接】。本次【链接】施加12点【护甲】</t>
   </si>
   <si>
+    <t>贯脉</t>
+  </si>
+  <si>
     <t>【链接】。穿透所有敌人则再次【链接】</t>
   </si>
   <si>
+    <t>LinkSwordsRepeat</t>
+  </si>
+  <si>
+    <t>缠丝</t>
+  </si>
+  <si>
     <t>【链接】。对【链接】的敌人施加2层【虚弱】，穿透所有敌人则再施加1层【易伤】</t>
   </si>
   <si>
+    <t>LinkDebuff</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>分野</t>
+  </si>
+  <si>
     <t>【链接】。穿透所有敌人则获得1点能量</t>
   </si>
   <si>
+    <t>扫弦</t>
+  </si>
+  <si>
     <t>【链接】。对【链接】的敌人施加2层【易伤】，穿透所有敌人则抽2张牌</t>
   </si>
   <si>
+    <t>天罗</t>
+  </si>
+  <si>
     <t>【链接】。【消耗】所有【护甲】，对全体敌人造成等量伤害。穿透所有敌人则恢复一半【护甲】</t>
   </si>
   <si>
+    <t>LinkSacrificeBlock</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>北斗</t>
+  </si>
+  <si>
     <t>【链接】均视为穿透所有敌人。【消耗】</t>
   </si>
   <si>
+    <t>LinkAlwaysPenetrate</t>
+  </si>
+  <si>
+    <t>空弦</t>
+  </si>
+  <si>
     <t>【链接】。不获得【护甲】，每【链接】1名敌人获得1点能量</t>
   </si>
   <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>PerLinkedEnemyEnergy</t>
+  </si>
+  <si>
+    <t>初照</t>
+  </si>
+  <si>
     <t>【链接】。穿透所有敌人则全体造成4点伤害</t>
   </si>
   <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>离身</t>
+  </si>
+  <si>
     <t>【链接】。随机去除1个负面效果</t>
   </si>
   <si>
+    <t>PurgeRandomDebuff</t>
+  </si>
+  <si>
+    <t>连丝</t>
+  </si>
+  <si>
     <t>【链接】。抽1张牌，弃1张手牌</t>
   </si>
   <si>
-    <t>如果处于停止则【旋剑】，抽1张牌；如果处于【旋剑】则停止且获得3点能量</t>
-  </si>
-  <si>
-    <t>手牌内所有含有【旋剑】的牌费用减1</t>
-  </si>
-  <si>
-    <t>【旋剑】。人剑合一获得1点能量</t>
-  </si>
-  <si>
-    <t>【旋剑】。抽1张牌，弃掉1张手牌</t>
-  </si>
-  <si>
-    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
-  </si>
-  <si>
-    <t>【剑来】。对途经敌人造成1次完整【旋剑】伤害随后停止</t>
-  </si>
-  <si>
-    <t>【旋剑】。对剑格敌人造成5*(X+1)点伤害</t>
-  </si>
-  <si>
-    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
-  </si>
-  <si>
-    <t>【御剑】且不停止【旋剑】状态</t>
-  </si>
-  <si>
-    <t>【旋剑】对邻格也造成伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>【旋剑】4次</t>
-  </si>
-  <si>
-    <t>造成4点伤害。【旋剑】</t>
-  </si>
-  <si>
-    <t>立即对剑格以及邻格敌人造成【旋剑】伤害</t>
-  </si>
-  <si>
-    <t>【旋剑】2次。人剑合一则随机对1名敌人造成【旋剑】伤害</t>
-  </si>
-  <si>
-    <t>【御剑】。如果移动到【灵剑】位置则摧毁【灵剑】，获得1能量并立即返回手牌</t>
-  </si>
-  <si>
-    <t>【御剑】控制所有【灵剑】至目标之后摧毁，每一道【灵剑】对目标造成11点伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>【御剑】。对目标位置造成8点伤害。如果存在【灵剑】，摧毁并造成18点伤害</t>
-  </si>
-  <si>
-    <t>【剑来】。抽1张牌，如果摧毁【灵剑】获得1点能量</t>
-  </si>
-  <si>
-    <t>【剑来】。如果摧毁【灵剑】，抽1张牌</t>
-  </si>
-  <si>
-    <t>【剑来】。每摧毁1道【灵剑】获得1能量并抽1张牌</t>
-  </si>
-  <si>
-    <t>【遁形】1距离。如果移动到【灵剑】位置摧毁【灵剑】，获得12【护甲】</t>
-  </si>
-  <si>
-    <t>【遁形】到【飞剑】/【灵剑】。如果到【飞剑】位置获得9【护甲】；如果到【灵剑】位置，摧毁并获得18【护甲】</t>
-  </si>
-  <si>
-    <t>所有正在【旋剑】的【飞剑】和【灵剑】伤害翻倍</t>
-  </si>
-  <si>
-    <t>【旋剑】会对【灵剑】一起生效。【消耗】</t>
-  </si>
-  <si>
-    <t>每摧毁2把【灵剑】就随机在空位置生成一道【灵剑】。【消耗】</t>
-  </si>
-  <si>
-    <t>随机在3处空位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>每回合开始随机位置生成一道【灵剑】。【灵剑】途经造成9点伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>摧毁指定位置的【灵剑】，恢复能量至上限</t>
+    <t>凝雪</t>
   </si>
   <si>
     <t>【链接】。对所有【链接】【灵剑】的位置造成6点伤害</t>
   </si>
   <si>
-    <t>【附着·灵】。如果已经附着【灵剑】，恢复7点生命值</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着，在指定位置生成【灵剑】。【剑来】</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着剑灵，在指定位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>御剑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>剑来</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bear</t>
+    <t>LinkSpiritDamage</t>
+  </si>
+  <si>
+    <t>【御剑】。如果飞剑移动到【灵剑】位置则摧毁【灵剑】，获得1能量并立即返回手牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -502,17 +817,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -555,7 +869,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -833,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -847,7 +1161,7 @@
     <col min="9" max="9" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -875,1402 +1189,3088 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>12002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" t="s">
+        <v>72</v>
+      </c>
+      <c r="P6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>73</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>12004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" t="s">
+        <v>81</v>
+      </c>
+      <c r="W8" t="s">
+        <v>64</v>
+      </c>
+      <c r="X8" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" t="s">
+        <v>72</v>
+      </c>
+      <c r="U9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>122</v>
+        <v>86</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>252</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" t="s">
+        <v>72</v>
+      </c>
+      <c r="P10" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>88</v>
+      </c>
+      <c r="R10" t="s">
+        <v>64</v>
+      </c>
+      <c r="U10" t="s">
+        <v>87</v>
+      </c>
+      <c r="V10" t="s">
+        <v>89</v>
+      </c>
+      <c r="W10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>12007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" t="s">
+        <v>93</v>
+      </c>
+      <c r="P11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>94</v>
+      </c>
+      <c r="R11" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>59</v>
+      </c>
+      <c r="R12" t="s">
+        <v>60</v>
+      </c>
+      <c r="S12" t="s">
+        <v>98</v>
+      </c>
+      <c r="U12" t="s">
+        <v>87</v>
+      </c>
+      <c r="V12" t="s">
+        <v>89</v>
+      </c>
+      <c r="W12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>54</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J13" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" t="s">
+        <v>103</v>
+      </c>
+      <c r="M13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N13" t="s">
+        <v>104</v>
+      </c>
+      <c r="P13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>81</v>
+      </c>
+      <c r="R15" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" t="s">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J16" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" t="s">
+        <v>104</v>
+      </c>
+      <c r="P16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>12012</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J17" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" t="s">
+        <v>64</v>
+      </c>
+      <c r="N17" t="s">
+        <v>117</v>
+      </c>
+      <c r="P17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>12013</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K18" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" t="s">
+        <v>107</v>
+      </c>
+      <c r="M18" t="s">
+        <v>64</v>
+      </c>
+      <c r="P18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>103</v>
+      </c>
+      <c r="R18" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>12014</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J19" t="s">
+        <v>62</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19" t="s">
+        <v>64</v>
+      </c>
+      <c r="N19" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>123</v>
+      </c>
+      <c r="R19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J20" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" t="s">
+        <v>104</v>
+      </c>
+      <c r="P20" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>94</v>
+      </c>
+      <c r="R20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" t="s">
+        <v>129</v>
+      </c>
+      <c r="M21" t="s">
+        <v>64</v>
+      </c>
+      <c r="P21" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>130</v>
+      </c>
+      <c r="R21" t="s">
+        <v>64</v>
+      </c>
+      <c r="U21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J22" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" t="s">
+        <v>71</v>
+      </c>
+      <c r="M22" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>81</v>
+      </c>
+      <c r="R22" t="s">
+        <v>64</v>
+      </c>
+      <c r="S22" t="s">
+        <v>72</v>
+      </c>
+      <c r="U22" t="s">
+        <v>133</v>
+      </c>
+      <c r="V22" t="s">
+        <v>107</v>
+      </c>
+      <c r="W22" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" t="s">
+        <v>71</v>
+      </c>
+      <c r="M23" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" t="s">
+        <v>72</v>
+      </c>
+      <c r="P23" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>107</v>
+      </c>
+      <c r="R23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J24" t="s">
+        <v>62</v>
+      </c>
+      <c r="K24" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" t="s">
+        <v>138</v>
+      </c>
+      <c r="M24" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" t="s">
+        <v>72</v>
+      </c>
+      <c r="P24" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>139</v>
+      </c>
+      <c r="R24" t="s">
+        <v>64</v>
+      </c>
+      <c r="S24" t="s">
+        <v>72</v>
+      </c>
+      <c r="U24" t="s">
+        <v>133</v>
+      </c>
+      <c r="V24" t="s">
+        <v>107</v>
+      </c>
+      <c r="W24" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" t="s">
+        <v>103</v>
+      </c>
+      <c r="M25" t="s">
+        <v>64</v>
+      </c>
+      <c r="N25" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>89</v>
+      </c>
+      <c r="R25" t="s">
+        <v>64</v>
+      </c>
+      <c r="U25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J26" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" t="s">
+        <v>103</v>
+      </c>
+      <c r="M26" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" t="s">
+        <v>77</v>
+      </c>
+      <c r="P26" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>103</v>
+      </c>
+      <c r="R26" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" t="s">
+        <v>98</v>
+      </c>
+      <c r="U26" t="s">
+        <v>87</v>
+      </c>
+      <c r="V26" t="s">
+        <v>89</v>
+      </c>
+      <c r="W26" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K27" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" t="s">
+        <v>148</v>
+      </c>
+      <c r="M27" t="s">
+        <v>64</v>
+      </c>
+      <c r="P27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>149</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J28" t="s">
+        <v>62</v>
+      </c>
+      <c r="K28" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" t="s">
+        <v>151</v>
+      </c>
+      <c r="M28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" t="s">
+        <v>154</v>
+      </c>
+      <c r="M29" t="s">
+        <v>64</v>
+      </c>
+      <c r="P29" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>81</v>
+      </c>
+      <c r="R29" t="s">
+        <v>64</v>
+      </c>
+      <c r="S29" t="s">
+        <v>72</v>
+      </c>
+      <c r="U29" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J30" t="s">
+        <v>62</v>
+      </c>
+      <c r="K30" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" t="s">
+        <v>154</v>
+      </c>
+      <c r="M30" t="s">
+        <v>64</v>
+      </c>
+      <c r="P30" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" t="s">
+        <v>64</v>
+      </c>
+      <c r="S30" t="s">
+        <v>72</v>
+      </c>
+      <c r="U30" t="s">
+        <v>62</v>
+      </c>
+      <c r="V30" t="s">
+        <v>157</v>
+      </c>
+      <c r="W30" t="s">
+        <v>64</v>
+      </c>
+      <c r="X30" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>112</v>
+        <v>159</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J31" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" t="s">
+        <v>154</v>
+      </c>
+      <c r="M31" t="s">
+        <v>64</v>
+      </c>
+      <c r="P31" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>107</v>
+      </c>
+      <c r="R31" t="s">
+        <v>64</v>
+      </c>
+      <c r="U31" t="s">
+        <v>62</v>
+      </c>
+      <c r="V31" t="s">
+        <v>160</v>
+      </c>
+      <c r="W31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>113</v>
+        <v>69</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J32" t="s">
+        <v>62</v>
+      </c>
+      <c r="K32" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" t="s">
+        <v>64</v>
+      </c>
+      <c r="P32" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>164</v>
+      </c>
+      <c r="R32" t="s">
+        <v>64</v>
+      </c>
+      <c r="U32" t="s">
+        <v>62</v>
+      </c>
+      <c r="V32" t="s">
+        <v>107</v>
+      </c>
+      <c r="W32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="C33">
         <v>-1</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>114</v>
+        <v>166</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J33" t="s">
+        <v>62</v>
+      </c>
+      <c r="K33" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" t="s">
+        <v>154</v>
+      </c>
+      <c r="M33" t="s">
+        <v>64</v>
+      </c>
+      <c r="P33" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>167</v>
+      </c>
+      <c r="R33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J34" t="s">
+        <v>62</v>
+      </c>
+      <c r="K34" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" t="s">
+        <v>64</v>
+      </c>
+      <c r="P34" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>164</v>
+      </c>
+      <c r="R34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J35" t="s">
+        <v>57</v>
+      </c>
+      <c r="K35" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" t="s">
+        <v>64</v>
+      </c>
+      <c r="N35" t="s">
+        <v>173</v>
+      </c>
+      <c r="P35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J36" t="s">
+        <v>62</v>
+      </c>
+      <c r="K36" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36" t="s">
+        <v>64</v>
+      </c>
+      <c r="N36" t="s">
+        <v>176</v>
+      </c>
+      <c r="P36" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>94</v>
+      </c>
+      <c r="R36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J37" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" t="s">
+        <v>179</v>
+      </c>
+      <c r="M37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>58</v>
+        <v>180</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J38" t="s">
+        <v>62</v>
+      </c>
+      <c r="K38" t="s">
+        <v>58</v>
+      </c>
+      <c r="L38" t="s">
+        <v>154</v>
+      </c>
+      <c r="M38" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" t="s">
+        <v>182</v>
+      </c>
+      <c r="P38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J39" t="s">
+        <v>62</v>
+      </c>
+      <c r="K39" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" t="s">
+        <v>59</v>
+      </c>
+      <c r="M39" t="s">
+        <v>60</v>
+      </c>
+      <c r="N39" t="s">
+        <v>182</v>
+      </c>
+      <c r="P39" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>154</v>
+      </c>
+      <c r="R39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J40" t="s">
+        <v>62</v>
+      </c>
+      <c r="K40" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" t="s">
+        <v>170</v>
+      </c>
+      <c r="M40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J41" t="s">
+        <v>62</v>
+      </c>
+      <c r="K41" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" t="s">
+        <v>154</v>
+      </c>
+      <c r="M41" t="s">
+        <v>64</v>
+      </c>
+      <c r="N41" t="s">
+        <v>116</v>
+      </c>
+      <c r="P41" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>189</v>
+      </c>
+      <c r="R41" t="s">
+        <v>64</v>
+      </c>
+      <c r="U41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J42" t="s">
+        <v>62</v>
+      </c>
+      <c r="K42" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" t="s">
+        <v>63</v>
+      </c>
+      <c r="M42" t="s">
+        <v>64</v>
+      </c>
+      <c r="N42" t="s">
+        <v>192</v>
+      </c>
+      <c r="P42" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>94</v>
+      </c>
+      <c r="R42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>137</v>
+        <v>69</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J43" t="s">
+        <v>62</v>
+      </c>
+      <c r="K43" t="s">
+        <v>58</v>
+      </c>
+      <c r="L43" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" t="s">
+        <v>195</v>
+      </c>
+      <c r="P43" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>196</v>
+      </c>
+      <c r="R43" t="s">
+        <v>64</v>
+      </c>
+      <c r="S43" t="s">
+        <v>104</v>
+      </c>
+      <c r="U43" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>198</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>23</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>132</v>
+        <v>69</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J44" t="s">
+        <v>62</v>
+      </c>
+      <c r="K44" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" t="s">
+        <v>200</v>
+      </c>
+      <c r="P44" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>94</v>
+      </c>
+      <c r="R44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>65</v>
+        <v>201</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J45" t="s">
+        <v>62</v>
+      </c>
+      <c r="K45" t="s">
+        <v>58</v>
+      </c>
+      <c r="L45" t="s">
+        <v>203</v>
+      </c>
+      <c r="M45" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" t="s">
+        <v>204</v>
+      </c>
+      <c r="P45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>138</v>
+        <v>54</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>206</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J46" t="s">
+        <v>207</v>
+      </c>
+      <c r="K46" t="s">
+        <v>58</v>
+      </c>
+      <c r="L46" t="s">
+        <v>207</v>
+      </c>
+      <c r="M46" t="s">
+        <v>64</v>
+      </c>
+      <c r="N46" t="s">
+        <v>195</v>
+      </c>
+      <c r="P46" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>63</v>
+      </c>
+      <c r="R46" t="s">
+        <v>64</v>
+      </c>
+      <c r="S46" t="s">
+        <v>195</v>
+      </c>
+      <c r="U46" t="s">
+        <v>62</v>
+      </c>
+      <c r="V46" t="s">
+        <v>107</v>
+      </c>
+      <c r="W46" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J47" t="s">
+        <v>207</v>
+      </c>
+      <c r="K47" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" t="s">
+        <v>64</v>
+      </c>
+      <c r="N47" t="s">
+        <v>195</v>
+      </c>
+      <c r="P47" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>207</v>
+      </c>
+      <c r="R47" t="s">
+        <v>64</v>
+      </c>
+      <c r="U47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>67</v>
+        <v>210</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>134</v>
+        <v>211</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J48" t="s">
+        <v>62</v>
+      </c>
+      <c r="K48" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" t="s">
+        <v>63</v>
+      </c>
+      <c r="M48" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" t="s">
+        <v>212</v>
+      </c>
+      <c r="P48" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>126</v>
+      </c>
+      <c r="R48" t="s">
+        <v>64</v>
+      </c>
+      <c r="S48" t="s">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s">
+        <v>62</v>
+      </c>
+      <c r="V48" t="s">
+        <v>94</v>
+      </c>
+      <c r="W48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>135</v>
+        <v>69</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J49" t="s">
+        <v>89</v>
+      </c>
+      <c r="K49" t="s">
+        <v>58</v>
+      </c>
+      <c r="L49" t="s">
+        <v>215</v>
+      </c>
+      <c r="M49" t="s">
+        <v>64</v>
+      </c>
+      <c r="P49" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>89</v>
+      </c>
+      <c r="R49" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="G50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J50" t="s">
+        <v>62</v>
+      </c>
+      <c r="K50" t="s">
+        <v>58</v>
+      </c>
+      <c r="L50" t="s">
+        <v>80</v>
+      </c>
+      <c r="M50" t="s">
+        <v>64</v>
+      </c>
+      <c r="N50" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="P50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>12046</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>98</v>
+        <v>219</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J51" t="s">
+        <v>62</v>
+      </c>
+      <c r="K51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" t="s">
+        <v>220</v>
+      </c>
+      <c r="M51" t="s">
+        <v>64</v>
+      </c>
+      <c r="P51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>221</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E52" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J52" t="s">
+        <v>62</v>
+      </c>
+      <c r="K52" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" t="s">
+        <v>80</v>
+      </c>
+      <c r="M52" t="s">
+        <v>64</v>
+      </c>
+      <c r="P52" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>223</v>
+      </c>
+      <c r="R52" t="s">
+        <v>64</v>
+      </c>
+      <c r="S52" t="s">
+        <v>224</v>
+      </c>
+      <c r="T52" t="s">
+        <v>116</v>
+      </c>
+      <c r="U52" t="s">
+        <v>62</v>
+      </c>
+      <c r="V52" t="s">
+        <v>223</v>
+      </c>
+      <c r="W52" t="s">
+        <v>64</v>
+      </c>
+      <c r="X52" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>100</v>
+        <v>227</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J53" t="s">
+        <v>62</v>
+      </c>
+      <c r="K53" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" t="s">
+        <v>80</v>
+      </c>
+      <c r="M53" t="s">
+        <v>64</v>
+      </c>
+      <c r="P53" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>81</v>
+      </c>
+      <c r="R53" t="s">
+        <v>64</v>
+      </c>
+      <c r="S53" t="s">
+        <v>72</v>
+      </c>
+      <c r="U53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J54" t="s">
+        <v>62</v>
+      </c>
+      <c r="K54" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" t="s">
+        <v>80</v>
+      </c>
+      <c r="M54" t="s">
+        <v>64</v>
+      </c>
+      <c r="P54" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>223</v>
+      </c>
+      <c r="R54" t="s">
+        <v>64</v>
+      </c>
+      <c r="S54" t="s">
+        <v>225</v>
+      </c>
+      <c r="T54" t="s">
+        <v>116</v>
+      </c>
+      <c r="U54" t="s">
+        <v>62</v>
+      </c>
+      <c r="V54" t="s">
+        <v>71</v>
+      </c>
+      <c r="W54" t="s">
+        <v>64</v>
+      </c>
+      <c r="X54" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>102</v>
+        <v>231</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J55" t="s">
+        <v>62</v>
+      </c>
+      <c r="K55" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" t="s">
+        <v>232</v>
+      </c>
+      <c r="M55" t="s">
+        <v>64</v>
+      </c>
+      <c r="N55" t="s">
+        <v>58</v>
+      </c>
+      <c r="O55" t="s">
+        <v>233</v>
+      </c>
+      <c r="P55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>103</v>
+        <v>235</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J56" t="s">
+        <v>62</v>
+      </c>
+      <c r="K56" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" t="s">
+        <v>64</v>
+      </c>
+      <c r="N56" t="s">
+        <v>236</v>
+      </c>
+      <c r="P56" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>94</v>
+      </c>
+      <c r="R56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>76</v>
+        <v>237</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J57" t="s">
+        <v>62</v>
+      </c>
+      <c r="K57" t="s">
+        <v>58</v>
+      </c>
+      <c r="L57" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" t="s">
+        <v>64</v>
+      </c>
+      <c r="N57" t="s">
+        <v>239</v>
+      </c>
+      <c r="P57" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>240</v>
+      </c>
+      <c r="R57" t="s">
+        <v>64</v>
+      </c>
+      <c r="S57" t="s">
+        <v>72</v>
+      </c>
+      <c r="U57" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>105</v>
+        <v>242</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J58" t="s">
+        <v>62</v>
+      </c>
+      <c r="K58" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58" t="s">
+        <v>80</v>
+      </c>
+      <c r="M58" t="s">
+        <v>64</v>
+      </c>
+      <c r="P58" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>59</v>
+      </c>
+      <c r="R58" t="s">
+        <v>243</v>
+      </c>
+      <c r="S58" t="s">
+        <v>182</v>
+      </c>
+      <c r="U58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J59" t="s">
+        <v>62</v>
+      </c>
+      <c r="K59" t="s">
+        <v>58</v>
+      </c>
+      <c r="L59" t="s">
+        <v>80</v>
+      </c>
+      <c r="M59" t="s">
+        <v>64</v>
+      </c>
+      <c r="P59" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>246</v>
+      </c>
+      <c r="R59" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J60" t="s">
+        <v>62</v>
+      </c>
+      <c r="K60" t="s">
+        <v>58</v>
+      </c>
+      <c r="L60" t="s">
+        <v>80</v>
+      </c>
+      <c r="M60" t="s">
+        <v>64</v>
+      </c>
+      <c r="P60" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>71</v>
+      </c>
+      <c r="R60" t="s">
+        <v>64</v>
+      </c>
+      <c r="S60" t="s">
+        <v>72</v>
+      </c>
+      <c r="U60" t="s">
+        <v>62</v>
+      </c>
+      <c r="V60" t="s">
+        <v>157</v>
+      </c>
+      <c r="W60" t="s">
+        <v>64</v>
+      </c>
+      <c r="X60" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>142</v>
+        <v>56</v>
+      </c>
+      <c r="J61" t="s">
+        <v>62</v>
+      </c>
+      <c r="K61" t="s">
+        <v>58</v>
+      </c>
+      <c r="L61" t="s">
+        <v>80</v>
+      </c>
+      <c r="M61" t="s">
+        <v>64</v>
+      </c>
+      <c r="P61" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>251</v>
+      </c>
+      <c r="R61" t="s">
+        <v>64</v>
+      </c>
+      <c r="S61" t="s">
+        <v>61</v>
+      </c>
+      <c r="U61" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048A2E17-0189-4A30-91EC-AD4E51A9B2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0662DE-53CB-4398-A64A-FAB773146A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="254">
   <si>
     <t>CardId</t>
   </si>
@@ -202,7 +202,7 @@
     <t>普通</t>
   </si>
   <si>
-    <t>造成6点伤害，【御剑】至该格但不造成途经伤害。</t>
+    <t>造成6点伤害\n【御剑】但不造成途经伤害</t>
   </si>
   <si>
     <t>bear</t>
@@ -247,7 +247,7 @@
     <t>罕见</t>
   </si>
   <si>
-    <t>【御剑】到随机位置，抽1张牌</t>
+    <t>抽1张牌\n【御剑】到随机位置</t>
   </si>
   <si>
     <t>DrawCards</t>
@@ -262,538 +262,545 @@
     <t>惊鸿</t>
   </si>
   <si>
-    <t>【御剑】。如果【御剑】到邻格则造成9点途经伤害</t>
+    <t>【御剑】\n如果【御剑】距离不大于1则此次途经伤害+4</t>
   </si>
   <si>
     <t>PathDamageIfAdjacent</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>穿云</t>
+  </si>
+  <si>
+    <t>LinkSwords</t>
+  </si>
+  <si>
+    <t>GainEnergy</t>
+  </si>
+  <si>
+    <t>Penetrated</t>
+  </si>
+  <si>
+    <t>剑罡</t>
+  </si>
+  <si>
+    <t>【御剑】\n【链接】\n抽1张牌</t>
+  </si>
+  <si>
+    <t>逐星</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>【御剑】\n如果飞剑移动到【灵剑】位置则摧毁【灵剑】，获得1能量并再次返回手牌</t>
+  </si>
+  <si>
+    <t>SlotHasSpiritSword</t>
+  </si>
+  <si>
+    <t>ReturnToHand</t>
+  </si>
+  <si>
+    <t>DestroySpirit</t>
+  </si>
+  <si>
+    <t>万剑诀</t>
+  </si>
+  <si>
+    <t>能力</t>
+  </si>
+  <si>
+    <t>【御剑】控制所有【灵剑】至目标之后摧毁，每一道【灵剑】对目标造成11点伤害\n【消耗】</t>
+  </si>
+  <si>
+    <t>RecallSpiritsOnSwordMove</t>
+  </si>
+  <si>
+    <t>SetRecallSpiritsDamage</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>连环</t>
+  </si>
+  <si>
+    <t>【御剑】\n对目标位置造成8点伤害\n摧毁目标位置【灵剑】再造成10点伤害</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>护体</t>
+  </si>
+  <si>
+    <t>技能</t>
+  </si>
+  <si>
+    <t>【遁形】1距离，获得7点【护甲】</t>
+  </si>
+  <si>
+    <t>MovePlayer</t>
+  </si>
+  <si>
+    <t>GainBlock</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>剑来</t>
+  </si>
+  <si>
+    <t>RecallSwords</t>
+  </si>
+  <si>
+    <t>并锋</t>
+  </si>
+  <si>
+    <t>获得1点能量，人剑合一再获得1点能量</t>
+  </si>
+  <si>
+    <t>ManSwordUnity</t>
+  </si>
+  <si>
+    <t>乾坤</t>
+  </si>
+  <si>
+    <t>【遁形】1距离\n如果【易位】获得7点【护甲】</t>
+  </si>
+  <si>
+    <t>SlotHasEnemy</t>
+  </si>
+  <si>
+    <t>步月</t>
+  </si>
+  <si>
+    <t>【遁形】2距离\n获得5点【护甲】</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>回风</t>
+  </si>
+  <si>
+    <t>【剑来】\n获得6点【护甲】</t>
+  </si>
+  <si>
+    <t>远遁</t>
+  </si>
+  <si>
+    <t>【遁形】到随机位置，获得10点【护甲】</t>
+  </si>
+  <si>
+    <t>MovePlayerRandom</t>
+  </si>
+  <si>
+    <t>游龙</t>
+  </si>
+  <si>
+    <t>【飞剑】途经伤害+3\n【消耗】</t>
+  </si>
+  <si>
+    <t>SetCustomPathDamage</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Exhaust</t>
+  </si>
+  <si>
+    <t>遁影</t>
+  </si>
+  <si>
+    <t>【遁形】1距离\n如果【易位】【剑来】</t>
+  </si>
+  <si>
+    <t>RecallToSlot</t>
+  </si>
+  <si>
+    <t>MovePlayerToSlot</t>
+  </si>
+  <si>
+    <t>寒芒</t>
+  </si>
+  <si>
+    <t>【剑来】，抽1张牌\n如果摧毁任何【灵剑】获得1点能量</t>
+  </si>
+  <si>
+    <t>HasSpiritSword</t>
+  </si>
+  <si>
+    <t>追魂</t>
+  </si>
+  <si>
+    <t>【剑来】\n如果摧毁【灵剑】，抽1张牌</t>
+  </si>
+  <si>
+    <t>聚灵</t>
+  </si>
+  <si>
+    <t>【剑来】\n每摧毁1道【灵剑】获得1能量并抽1张牌</t>
+  </si>
+  <si>
+    <t>PerSpiritEnergy</t>
+  </si>
+  <si>
+    <t>PerSpiritDraw</t>
+  </si>
+  <si>
+    <t>灵遁</t>
+  </si>
+  <si>
+    <t>【遁形】1距离\n如果移动到【灵剑】位置摧毁【灵剑】，获得12【护甲】</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>剑翼</t>
+  </si>
+  <si>
+    <t>【遁形】到【飞剑】/【灵剑】\n到【飞剑】位置获得9【护甲】\n到【灵剑】位置，摧毁并获得18【护甲】</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>穿云</t>
-  </si>
-  <si>
-    <t>【御剑】并对目标位置造成6点伤害，之后【链接】。穿透所有敌人则获得1点能量</t>
-  </si>
-  <si>
-    <t>LinkSwords</t>
-  </si>
-  <si>
-    <t>GainEnergy</t>
-  </si>
-  <si>
-    <t>Penetrated</t>
-  </si>
-  <si>
-    <t>剑罡</t>
-  </si>
-  <si>
-    <t>【御剑】。【链接】。抽1张牌</t>
-  </si>
-  <si>
-    <t>逐星</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>SlotHasSpiritSword</t>
-  </si>
-  <si>
-    <t>ReturnToHand</t>
-  </si>
-  <si>
-    <t>DestroySpirit</t>
-  </si>
-  <si>
-    <t>万剑诀</t>
-  </si>
-  <si>
-    <t>能力</t>
-  </si>
-  <si>
-    <t>【御剑】控制所有【灵剑】至目标之后摧毁，每一道【灵剑】对目标造成11点伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>RecallSpiritsOnSwordMove</t>
-  </si>
-  <si>
-    <t>Exhaust</t>
-  </si>
-  <si>
-    <t>连环</t>
-  </si>
-  <si>
-    <t>【御剑】。对目标位置造成8点伤害。如果存在【灵剑】，摧毁并造成18点伤害</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>SlotHasSword</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>护体</t>
-  </si>
-  <si>
-    <t>技能</t>
-  </si>
-  <si>
-    <t>【遁形】1距离，获得7点【护甲】</t>
-  </si>
-  <si>
-    <t>MovePlayer</t>
-  </si>
-  <si>
-    <t>GainBlock</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>剑来</t>
+    <t>天罡</t>
+  </si>
+  <si>
+    <t>如果处于停止则【旋剑】，抽1张牌\n如果处于【旋剑】则停止，获得3点能量</t>
+  </si>
+  <si>
+    <t>TianGang</t>
+  </si>
+  <si>
+    <t>藏锋</t>
+  </si>
+  <si>
+    <t>手牌内所有含有【旋剑】的牌费用减1</t>
+  </si>
+  <si>
+    <t>ReduceSpinCost</t>
+  </si>
+  <si>
+    <t>重铸</t>
+  </si>
+  <si>
+    <t>【旋剑】\n人剑合一获得1点能量</t>
+  </si>
+  <si>
+    <t>SpinSword</t>
+  </si>
+  <si>
+    <t>崩锋</t>
+  </si>
+  <si>
+    <t>【旋剑】\n抽1张牌，弃掉1张手牌</t>
+  </si>
+  <si>
+    <t>InteractiveDiscard</t>
+  </si>
+  <si>
+    <t>御风</t>
+  </si>
+  <si>
+    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
+  </si>
+  <si>
+    <t>GainSpinBlock</t>
+  </si>
+  <si>
+    <t>化莲</t>
+  </si>
+  <si>
+    <t>【剑来】\n对途经敌人造成1次完整【旋剑】伤害随后停止</t>
+  </si>
+  <si>
+    <t>RecallSpinDamage</t>
+  </si>
+  <si>
+    <t>StopSpin</t>
+  </si>
+  <si>
+    <t>断江</t>
+  </si>
+  <si>
+    <t>【旋剑】\n对剑格敌人造成5*(X+1)点伤害</t>
+  </si>
+  <si>
+    <t>SpinFormulaDamage</t>
+  </si>
+  <si>
+    <t>横舟</t>
+  </si>
+  <si>
+    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
+  </si>
+  <si>
+    <t>SpinDamageImmediate</t>
+  </si>
+  <si>
+    <t>赶月</t>
+  </si>
+  <si>
+    <t>【御剑】且不停止【旋剑】状态</t>
+  </si>
+  <si>
+    <t>KeepSpinningOnMove</t>
+  </si>
+  <si>
+    <t>流光</t>
+  </si>
+  <si>
+    <t>【旋剑】对邻格也造成伤害\n【消耗】</t>
+  </si>
+  <si>
+    <t>SpinHitsAdjacent</t>
+  </si>
+  <si>
+    <t>刹那</t>
+  </si>
+  <si>
+    <t>当前正在【旋剑】的【飞剑】和【灵剑】伤害翻倍</t>
+  </si>
+  <si>
+    <t>DoubleSpinDamage</t>
+  </si>
+  <si>
+    <t>天华</t>
+  </si>
+  <si>
+    <t>【旋剑】4次</t>
+  </si>
+  <si>
+    <t>铸芒</t>
+  </si>
+  <si>
+    <t>造成4点伤害\n【旋剑】</t>
+  </si>
+  <si>
+    <t>碎星</t>
+  </si>
+  <si>
+    <t>立即对剑格和邻格敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>白虹</t>
+  </si>
+  <si>
+    <t>【旋剑】2次\n人剑合一则随机对1名敌人造成【旋剑】伤害</t>
+  </si>
+  <si>
+    <t>SpinDamageRandomEnemy</t>
+  </si>
+  <si>
+    <t>星河</t>
+  </si>
+  <si>
+    <t>【旋剑】会对【灵剑】一起生效\n【消耗】</t>
+  </si>
+  <si>
+    <t>SpinAffectsSpirits</t>
+  </si>
+  <si>
+    <t>蚀髓</t>
+  </si>
+  <si>
+    <t>【附着·灵】\n如果已经附着【灵剑】，恢复7点生命值</t>
+  </si>
+  <si>
+    <t>IsSpiritAttached</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>SpiritAttached</t>
+  </si>
+  <si>
+    <t>碧海潮生</t>
+  </si>
+  <si>
+    <t>每摧毁1把【灵剑】就随机在空位置生成一道【灵剑】\n【消耗】</t>
+  </si>
+  <si>
+    <t>HasReactiveSpiritSpawn</t>
+  </si>
+  <si>
+    <t>种灵</t>
+  </si>
+  <si>
+    <t>随机在3处空位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>SpawnSpiritsRandom</t>
+  </si>
+  <si>
+    <t>御灵</t>
+  </si>
+  <si>
+    <t>【附着·灵】\n如果已经附着，在指定位置生成【灵剑】\n【剑来】</t>
+  </si>
+  <si>
+    <t>SpawnSpiritAtSlot</t>
+  </si>
+  <si>
+    <t>灵附</t>
+  </si>
+  <si>
+    <t>【附着·灵】\n如果已经附着剑灵，在指定位置生成【灵剑】</t>
+  </si>
+  <si>
+    <t>灵潮</t>
+  </si>
+  <si>
+    <t>每回合开始随机位置生成【灵剑】\n【灵剑】途经伤害+4\n【消耗】</t>
+  </si>
+  <si>
+    <t>HasTurnStartSpiritSpawn</t>
+  </si>
+  <si>
+    <t>归尘</t>
+  </si>
+  <si>
+    <t>摧毁指定位置的【灵剑】，获得等同于上限的能量值</t>
+  </si>
+  <si>
+    <t>GainMaxEnergy</t>
+  </si>
+  <si>
+    <t>牵络</t>
+  </si>
+  <si>
+    <t>贯脉</t>
+  </si>
+  <si>
+    <t>LinkSwordsRepeat</t>
+  </si>
+  <si>
+    <t>缠丝</t>
+  </si>
+  <si>
+    <t>LinkDebuff</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>分野</t>
+  </si>
+  <si>
+    <t>【链接】\n【穿透】则获得1点能量</t>
+  </si>
+  <si>
+    <t>扫弦</t>
+  </si>
+  <si>
+    <t>【链接】\n对【链接】的敌人施加2层【易伤】，【穿透】则抽2张牌</t>
+  </si>
+  <si>
+    <t>天罗</t>
+  </si>
+  <si>
+    <t>【链接】\n【消耗】所有【护甲】，对全体敌人造成等量伤害\n【穿透】则恢复一半【护甲】</t>
+  </si>
+  <si>
+    <t>LinkSacrificeBlock</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>北斗</t>
+  </si>
+  <si>
+    <t>【链接】均视为【穿透】\n【消耗】</t>
+  </si>
+  <si>
+    <t>LinkAlwaysPenetrate</t>
+  </si>
+  <si>
+    <t>织网</t>
+  </si>
+  <si>
+    <t>【链接】\n尝试在每个位置生成灵剑，每把灵剑消耗6护甲\n优先在敌人位置生成</t>
+  </si>
+  <si>
+    <t>SpawnSpiritsByArmor</t>
+  </si>
+  <si>
+    <t>初照</t>
+  </si>
+  <si>
+    <t>【链接】\n【穿透】则全体造成4点伤害</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>离身</t>
+  </si>
+  <si>
+    <t>【链接】\n随机去除1个负面效果</t>
+  </si>
+  <si>
+    <t>PurgeRandomDebuff</t>
+  </si>
+  <si>
+    <t>连丝</t>
+  </si>
+  <si>
+    <t>【链接】\n抽1张牌，弃1张手牌</t>
+  </si>
+  <si>
+    <t>凝雪</t>
+  </si>
+  <si>
+    <t>在指定位置生成【灵剑】\n对所有【灵剑】的位置的敌人造成7点伤害</t>
+  </si>
+  <si>
+    <t>SpiritPositionsDamage</t>
+  </si>
+  <si>
+    <t>【链接】\n本次【链接】施加12点【护甲】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【链接】\n【穿透】则再次【链接】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【链接】\n对【链接】的敌人施加2层【虚弱】，【穿透】则再施加1层【易伤】</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>【剑来】</t>
-  </si>
-  <si>
-    <t>RecallSwords</t>
-  </si>
-  <si>
-    <t>并锋</t>
-  </si>
-  <si>
-    <t>获得1点能量，人剑合一再获得1点能量</t>
-  </si>
-  <si>
-    <t>ManSwordUnity</t>
-  </si>
-  <si>
-    <t>乾坤</t>
-  </si>
-  <si>
-    <t>【遁形】1距离。如果与敌人【易位】，获得7点【护甲】</t>
-  </si>
-  <si>
-    <t>SlotHasEnemy</t>
-  </si>
-  <si>
-    <t>步月</t>
-  </si>
-  <si>
-    <t>【遁形】2距离。获得5点【护甲】</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>回风</t>
-  </si>
-  <si>
-    <t>【剑来】。获得6点【护甲】</t>
-  </si>
-  <si>
-    <t>远遁</t>
-  </si>
-  <si>
-    <t>【遁形】到随机位置，获得10点【护甲】</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>MovePlayerRandom</t>
-  </si>
-  <si>
-    <t>游龙</t>
-  </si>
-  <si>
-    <t>【飞剑】造成7点途经伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>SetCustomPathDamage</t>
-  </si>
-  <si>
-    <t>遁影</t>
-  </si>
-  <si>
-    <t>【遁形】1距离，如果【易位】则【剑来】</t>
-  </si>
-  <si>
-    <t>RecallToSlot</t>
-  </si>
-  <si>
-    <t>MovePlayerToSlot</t>
-  </si>
-  <si>
-    <t>寒芒</t>
-  </si>
-  <si>
-    <t>【剑来】。抽1张牌，如果摧毁任何【灵剑】获得1点能量</t>
-  </si>
-  <si>
-    <t>HasSpiritSword</t>
-  </si>
-  <si>
-    <t>追魂</t>
-  </si>
-  <si>
-    <t>【剑来】。如果摧毁【灵剑】，抽1张牌</t>
-  </si>
-  <si>
-    <t>聚灵</t>
-  </si>
-  <si>
-    <t>【剑来】。每摧毁1道【灵剑】获得1能量并抽1张牌</t>
-  </si>
-  <si>
-    <t>PerSpiritEnergy</t>
-  </si>
-  <si>
-    <t>PerSpiritDraw</t>
-  </si>
-  <si>
-    <t>灵遁</t>
-  </si>
-  <si>
-    <t>【遁形】1距离。如果移动到【灵剑】位置摧毁【灵剑】，获得12【护甲】</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>剑翼</t>
-  </si>
-  <si>
-    <t>【遁形】到【飞剑】/【灵剑】。如果到【飞剑】位置获得9【护甲】；如果到【灵剑】位置，摧毁并获得18【护甲】</t>
-  </si>
-  <si>
-    <t>SlotHasSword</t>
-  </si>
-  <si>
-    <t>天罡</t>
-  </si>
-  <si>
-    <t>如果处于停止则【旋剑】，抽1张牌；如果处于【旋剑】则停止且获得3点能量</t>
-  </si>
-  <si>
-    <t>TianGang</t>
-  </si>
-  <si>
-    <t>藏锋</t>
-  </si>
-  <si>
-    <t>手牌内所有含有【旋剑】的牌费用减1</t>
-  </si>
-  <si>
-    <t>ReduceSpinCost</t>
-  </si>
-  <si>
-    <t>重铸</t>
-  </si>
-  <si>
-    <t>【旋剑】。人剑合一获得1点能量</t>
-  </si>
-  <si>
-    <t>SpinSword</t>
-  </si>
-  <si>
-    <t>崩锋</t>
-  </si>
-  <si>
-    <t>【旋剑】。抽1张牌，弃掉1张手牌</t>
-  </si>
-  <si>
-    <t>InteractiveDiscard</t>
-  </si>
-  <si>
-    <t>御风</t>
-  </si>
-  <si>
-    <t>【旋剑】后【飞剑】瞬移至玩家位置，获得【旋剑】伤害等额【护甲】</t>
-  </si>
-  <si>
-    <t>GainSpinBlock</t>
-  </si>
-  <si>
-    <t>化莲</t>
-  </si>
-  <si>
-    <t>【剑来】。对途经敌人造成1次完整【旋剑】伤害随后停止</t>
-  </si>
-  <si>
-    <t>RecallSpinDamage</t>
-  </si>
-  <si>
-    <t>StopSpin</t>
-  </si>
-  <si>
-    <t>断江</t>
-  </si>
-  <si>
-    <t>【旋剑】。对剑格敌人造成5*(X+1)点伤害</t>
-  </si>
-  <si>
-    <t>SpinFormulaDamage</t>
-  </si>
-  <si>
-    <t>横舟</t>
-  </si>
-  <si>
-    <t>对敌人造成1次完整的【旋剑】伤害，停止</t>
-  </si>
-  <si>
-    <t>SpinDamageImmediate</t>
-  </si>
-  <si>
-    <t>赶月</t>
-  </si>
-  <si>
-    <t>【御剑】且不停止【旋剑】状态</t>
-  </si>
-  <si>
-    <t>KeepSpinningOnMove</t>
-  </si>
-  <si>
-    <t>流光</t>
-  </si>
-  <si>
-    <t>【旋剑】对邻格也造成伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>SpinHitsAdjacent</t>
-  </si>
-  <si>
-    <t>刹那</t>
-  </si>
-  <si>
-    <t>所有正在【旋剑】的【飞剑】和【灵剑】伤害翻倍</t>
-  </si>
-  <si>
-    <t>DoubleSpinDamage</t>
-  </si>
-  <si>
-    <t>天华</t>
-  </si>
-  <si>
-    <t>【旋剑】4次</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>铸芒</t>
-  </si>
-  <si>
-    <t>造成4点伤害。【旋剑】</t>
-  </si>
-  <si>
-    <t>碎星</t>
-  </si>
-  <si>
-    <t>立即对剑格以及邻格敌人造成【旋剑】伤害</t>
-  </si>
-  <si>
-    <t>白虹</t>
-  </si>
-  <si>
-    <t>【旋剑】2次。人剑合一则随机对1名敌人造成【旋剑】伤害</t>
-  </si>
-  <si>
-    <t>SpinDamageRandomEnemy</t>
-  </si>
-  <si>
-    <t>星河</t>
-  </si>
-  <si>
-    <t>【旋剑】会对【灵剑】一起生效。【消耗】</t>
-  </si>
-  <si>
-    <t>SpinAffectsSpirits</t>
-  </si>
-  <si>
-    <t>蚀髓</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着【灵剑】，恢复7点生命值</t>
-  </si>
-  <si>
-    <t>IsSpiritAttached</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>SpiritAttached</t>
-  </si>
-  <si>
-    <t>碧海潮生</t>
-  </si>
-  <si>
-    <t>每摧毁1把【灵剑】就随机在空位置生成一道【灵剑】。【消耗】</t>
-  </si>
-  <si>
-    <t>HasReactiveSpiritSpawn</t>
-  </si>
-  <si>
-    <t>种灵</t>
-  </si>
-  <si>
-    <t>随机在3处空位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>SpawnSpiritsRandom</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>御灵</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着，在指定位置生成【灵剑】。【剑来】</t>
-  </si>
-  <si>
-    <t>SpawnSpiritAtSlot</t>
-  </si>
-  <si>
-    <t>灵附</t>
-  </si>
-  <si>
-    <t>【附着·灵】。如果已经附着剑灵，在指定位置生成【灵剑】</t>
-  </si>
-  <si>
-    <t>灵潮</t>
-  </si>
-  <si>
-    <t>每回合开始随机位置生成一道【灵剑】。【灵剑】途经造成9点伤害。【消耗】</t>
-  </si>
-  <si>
-    <t>HasTurnStartSpiritSpawn</t>
-  </si>
-  <si>
-    <t>归尘</t>
-  </si>
-  <si>
-    <t>摧毁指定位置的【灵剑】，获得等同于上限的能量值</t>
-  </si>
-  <si>
-    <t>GainMaxEnergy</t>
-  </si>
-  <si>
-    <t>牵络</t>
-  </si>
-  <si>
-    <t>【链接】。本次【链接】施加12点【护甲】</t>
-  </si>
-  <si>
-    <t>贯脉</t>
-  </si>
-  <si>
-    <t>【链接】。穿透所有敌人则再次【链接】</t>
-  </si>
-  <si>
-    <t>LinkSwordsRepeat</t>
-  </si>
-  <si>
-    <t>缠丝</t>
-  </si>
-  <si>
-    <t>【链接】。对【链接】的敌人施加2层【虚弱】，穿透所有敌人则再施加1层【易伤】</t>
-  </si>
-  <si>
-    <t>LinkDebuff</t>
-  </si>
-  <si>
-    <t>Weak</t>
-  </si>
-  <si>
-    <t>Vulnerable</t>
-  </si>
-  <si>
-    <t>分野</t>
-  </si>
-  <si>
-    <t>【链接】。穿透所有敌人则获得1点能量</t>
-  </si>
-  <si>
-    <t>扫弦</t>
-  </si>
-  <si>
-    <t>【链接】。对【链接】的敌人施加2层【易伤】，穿透所有敌人则抽2张牌</t>
-  </si>
-  <si>
-    <t>天罗</t>
-  </si>
-  <si>
-    <t>【链接】。【消耗】所有【护甲】，对全体敌人造成等量伤害。穿透所有敌人则恢复一半【护甲】</t>
-  </si>
-  <si>
-    <t>LinkSacrificeBlock</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>北斗</t>
-  </si>
-  <si>
-    <t>【链接】均视为穿透所有敌人。【消耗】</t>
-  </si>
-  <si>
-    <t>LinkAlwaysPenetrate</t>
-  </si>
-  <si>
-    <t>空弦</t>
-  </si>
-  <si>
-    <t>【链接】。不获得【护甲】，每【链接】1名敌人获得1点能量</t>
-  </si>
-  <si>
-    <t>-1</t>
-  </si>
-  <si>
-    <t>PerLinkedEnemyEnergy</t>
-  </si>
-  <si>
-    <t>初照</t>
-  </si>
-  <si>
-    <t>【链接】。穿透所有敌人则全体造成4点伤害</t>
-  </si>
-  <si>
-    <t>AllEnemies</t>
-  </si>
-  <si>
-    <t>离身</t>
-  </si>
-  <si>
-    <t>【链接】。随机去除1个负面效果</t>
-  </si>
-  <si>
-    <t>PurgeRandomDebuff</t>
-  </si>
-  <si>
-    <t>连丝</t>
-  </si>
-  <si>
-    <t>【链接】。抽1张牌，弃1张手牌</t>
-  </si>
-  <si>
-    <t>凝雪</t>
-  </si>
-  <si>
-    <t>【链接】。对所有【链接】【灵剑】的位置造成6点伤害</t>
-  </si>
-  <si>
-    <t>LinkSpiritDamage</t>
-  </si>
-  <si>
-    <t>【御剑】。如果飞剑移动到【灵剑】位置则摧毁【灵剑】，获得1能量并立即返回手牌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>【御剑】并对目标位置造成6点伤害\n【链接】，【穿透】则获得1点能量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -851,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -872,6 +879,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1626,8 +1634,8 @@
       <c r="E8" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>79</v>
+      <c r="F8" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>56</v>
@@ -1651,16 +1659,16 @@
         <v>62</v>
       </c>
       <c r="Q8" t="s">
+        <v>79</v>
+      </c>
+      <c r="R8" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" t="s">
+        <v>62</v>
+      </c>
+      <c r="V8" t="s">
         <v>80</v>
-      </c>
-      <c r="R8" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" t="s">
-        <v>62</v>
-      </c>
-      <c r="V8" t="s">
-        <v>81</v>
       </c>
       <c r="W8" t="s">
         <v>64</v>
@@ -1669,7 +1677,7 @@
         <v>72</v>
       </c>
       <c r="Z8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.25">
@@ -1677,7 +1685,7 @@
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1689,7 +1697,7 @@
         <v>54</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>56</v>
@@ -1701,7 +1709,7 @@
         <v>58</v>
       </c>
       <c r="L9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M9" t="s">
         <v>64</v>
@@ -1727,7 +1735,7 @@
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1736,10 +1744,10 @@
         <v>53</v>
       </c>
       <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>56</v>
@@ -1751,7 +1759,7 @@
         <v>58</v>
       </c>
       <c r="L10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M10" t="s">
         <v>64</v>
@@ -1795,7 +1803,7 @@
         <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>92</v>
@@ -1826,6 +1834,9 @@
       </c>
       <c r="R11" t="s">
         <v>64</v>
+      </c>
+      <c r="S11" t="s">
+        <v>95</v>
       </c>
       <c r="U11" t="s">
         <v>62</v>
@@ -1836,7 +1847,7 @@
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1847,8 +1858,8 @@
       <c r="E12" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>96</v>
+      <c r="F12" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>56</v>
@@ -1866,7 +1877,7 @@
         <v>60</v>
       </c>
       <c r="N12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P12" t="s">
         <v>62</v>
@@ -1878,7 +1889,7 @@
         <v>60</v>
       </c>
       <c r="S12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U12" t="s">
         <v>87</v>
@@ -1898,37 +1909,37 @@
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>54</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K13" t="s">
         <v>72</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M13" t="s">
         <v>64</v>
       </c>
       <c r="N13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P13" t="s">
         <v>62</v>
@@ -1939,19 +1950,19 @@
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
         <v>54</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>56</v>
@@ -1980,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>54</v>
@@ -1998,7 +2009,7 @@
         <v>58</v>
       </c>
       <c r="L15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
         <v>64</v>
@@ -2010,7 +2021,7 @@
         <v>62</v>
       </c>
       <c r="Q15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R15" t="s">
         <v>64</v>
@@ -2033,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>54</v>
@@ -2045,19 +2056,19 @@
         <v>56</v>
       </c>
       <c r="J16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s">
         <v>72</v>
       </c>
       <c r="L16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M16" t="s">
         <v>64</v>
       </c>
       <c r="N16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P16" t="s">
         <v>113</v>
@@ -2074,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
         <v>54</v>
@@ -2086,13 +2097,13 @@
         <v>56</v>
       </c>
       <c r="J17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K17" t="s">
         <v>116</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M17" t="s">
         <v>64</v>
@@ -2115,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
         <v>54</v>
@@ -2142,7 +2153,7 @@
         <v>62</v>
       </c>
       <c r="Q18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R18" t="s">
         <v>64</v>
@@ -2165,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>69</v>
@@ -2183,19 +2194,19 @@
         <v>58</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M19" t="s">
         <v>64</v>
       </c>
       <c r="N19" t="s">
+        <v>99</v>
+      </c>
+      <c r="P19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q19" t="s">
         <v>122</v>
-      </c>
-      <c r="P19" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>123</v>
       </c>
       <c r="R19" t="s">
         <v>64</v>
@@ -2206,7 +2217,7 @@
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -2217,32 +2228,32 @@
       <c r="E20" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" t="s">
+        <v>62</v>
+      </c>
+      <c r="K20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" t="s">
         <v>125</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20" t="s">
-        <v>62</v>
-      </c>
-      <c r="K20" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" t="s">
         <v>126</v>
       </c>
-      <c r="M20" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20" t="s">
-        <v>104</v>
-      </c>
       <c r="P20" t="s">
         <v>62</v>
       </c>
       <c r="Q20" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="R20" t="s">
         <v>64</v>
@@ -2253,31 +2264,31 @@
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>128</v>
+      <c r="F21" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K21" t="s">
         <v>72</v>
       </c>
       <c r="L21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M21" t="s">
         <v>64</v>
@@ -2286,7 +2297,7 @@
         <v>113</v>
       </c>
       <c r="Q21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R21" t="s">
         <v>64</v>
@@ -2300,19 +2311,19 @@
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>56</v>
@@ -2336,7 +2347,7 @@
         <v>62</v>
       </c>
       <c r="Q22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R22" t="s">
         <v>64</v>
@@ -2345,7 +2356,7 @@
         <v>72</v>
       </c>
       <c r="U22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="V22" t="s">
         <v>107</v>
@@ -2362,19 +2373,19 @@
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>135</v>
+      <c r="F23" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>56</v>
@@ -2395,7 +2406,7 @@
         <v>72</v>
       </c>
       <c r="P23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q23" t="s">
         <v>107</v>
@@ -2409,19 +2420,19 @@
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>137</v>
+      <c r="F24" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>56</v>
@@ -2433,7 +2444,7 @@
         <v>58</v>
       </c>
       <c r="L24" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M24" t="s">
         <v>64</v>
@@ -2442,10 +2453,10 @@
         <v>72</v>
       </c>
       <c r="P24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R24" t="s">
         <v>64</v>
@@ -2454,7 +2465,7 @@
         <v>72</v>
       </c>
       <c r="U24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="V24" t="s">
         <v>107</v>
@@ -2471,37 +2482,37 @@
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>54</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s">
         <v>72</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M25" t="s">
         <v>64</v>
       </c>
       <c r="N25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P25" t="s">
         <v>87</v>
@@ -2521,49 +2532,49 @@
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>144</v>
+      <c r="F26" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K26" t="s">
         <v>58</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M26" t="s">
         <v>64</v>
       </c>
       <c r="N26" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R26" t="s">
         <v>64</v>
       </c>
       <c r="S26" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="U26" t="s">
         <v>87</v>
@@ -2583,19 +2594,19 @@
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>69</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>147</v>
+      <c r="F27" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>56</v>
@@ -2607,7 +2618,7 @@
         <v>58</v>
       </c>
       <c r="L27" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M27" t="s">
         <v>64</v>
@@ -2621,19 +2632,19 @@
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
         <v>69</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>56</v>
@@ -2645,7 +2656,7 @@
         <v>58</v>
       </c>
       <c r="L28" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M28" t="s">
         <v>64</v>
@@ -2656,7 +2667,7 @@
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2668,7 +2679,7 @@
         <v>54</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>56</v>
@@ -2680,7 +2691,7 @@
         <v>58</v>
       </c>
       <c r="L29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M29" t="s">
         <v>64</v>
@@ -2689,7 +2700,7 @@
         <v>62</v>
       </c>
       <c r="Q29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R29" t="s">
         <v>64</v>
@@ -2706,7 +2717,7 @@
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2718,7 +2729,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>56</v>
@@ -2730,7 +2741,7 @@
         <v>58</v>
       </c>
       <c r="L30" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M30" t="s">
         <v>64</v>
@@ -2751,7 +2762,7 @@
         <v>62</v>
       </c>
       <c r="V30" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="W30" t="s">
         <v>64</v>
@@ -2768,7 +2779,7 @@
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -2780,7 +2791,7 @@
         <v>69</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>56</v>
@@ -2792,7 +2803,7 @@
         <v>58</v>
       </c>
       <c r="L31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M31" t="s">
         <v>64</v>
@@ -2810,7 +2821,7 @@
         <v>62</v>
       </c>
       <c r="V31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="W31" t="s">
         <v>64</v>
@@ -2821,19 +2832,19 @@
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
         <v>69</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>56</v>
@@ -2845,7 +2856,7 @@
         <v>58</v>
       </c>
       <c r="L32" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M32" t="s">
         <v>64</v>
@@ -2854,7 +2865,7 @@
         <v>62</v>
       </c>
       <c r="Q32" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="R32" t="s">
         <v>64</v>
@@ -2874,7 +2885,7 @@
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -2886,7 +2897,7 @@
         <v>69</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>56</v>
@@ -2898,7 +2909,7 @@
         <v>58</v>
       </c>
       <c r="L33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M33" t="s">
         <v>64</v>
@@ -2907,7 +2918,7 @@
         <v>62</v>
       </c>
       <c r="Q33" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R33" t="s">
         <v>64</v>
@@ -2918,7 +2929,7 @@
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2930,7 +2941,7 @@
         <v>69</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>56</v>
@@ -2942,7 +2953,7 @@
         <v>58</v>
       </c>
       <c r="L34" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s">
         <v>64</v>
@@ -2951,7 +2962,7 @@
         <v>62</v>
       </c>
       <c r="Q34" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="R34" t="s">
         <v>64</v>
@@ -2962,7 +2973,7 @@
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2974,7 +2985,7 @@
         <v>54</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>56</v>
@@ -2992,7 +3003,7 @@
         <v>64</v>
       </c>
       <c r="N35" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P35" t="s">
         <v>62</v>
@@ -3003,7 +3014,7 @@
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3012,10 +3023,10 @@
         <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>56</v>
@@ -3033,13 +3044,13 @@
         <v>64</v>
       </c>
       <c r="N36" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P36" t="s">
         <v>62</v>
       </c>
       <c r="Q36" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="R36" t="s">
         <v>64</v>
@@ -3050,19 +3061,19 @@
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E37" t="s">
         <v>69</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>56</v>
@@ -3074,7 +3085,7 @@
         <v>58</v>
       </c>
       <c r="L37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M37" t="s">
         <v>64</v>
@@ -3085,7 +3096,7 @@
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -3097,7 +3108,7 @@
         <v>54</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>56</v>
@@ -3109,13 +3120,13 @@
         <v>58</v>
       </c>
       <c r="L38" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M38" t="s">
         <v>64</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="P38" t="s">
         <v>62</v>
@@ -3126,7 +3137,7 @@
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3138,7 +3149,7 @@
         <v>54</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>56</v>
@@ -3156,13 +3167,13 @@
         <v>60</v>
       </c>
       <c r="N39" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="P39" t="s">
         <v>62</v>
       </c>
       <c r="Q39" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="R39" t="s">
         <v>64</v>
@@ -3173,7 +3184,7 @@
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -3185,7 +3196,7 @@
         <v>69</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>56</v>
@@ -3197,7 +3208,7 @@
         <v>58</v>
       </c>
       <c r="L40" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M40" t="s">
         <v>64</v>
@@ -3208,7 +3219,7 @@
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -3220,7 +3231,7 @@
         <v>54</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>56</v>
@@ -3232,7 +3243,7 @@
         <v>58</v>
       </c>
       <c r="L41" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M41" t="s">
         <v>64</v>
@@ -3244,7 +3255,7 @@
         <v>62</v>
       </c>
       <c r="Q41" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R41" t="s">
         <v>64</v>
@@ -3258,7 +3269,7 @@
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -3267,10 +3278,10 @@
         <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>56</v>
@@ -3288,13 +3299,13 @@
         <v>64</v>
       </c>
       <c r="N42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P42" t="s">
         <v>62</v>
       </c>
       <c r="Q42" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="R42" t="s">
         <v>64</v>
@@ -3305,19 +3316,19 @@
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E43" t="s">
         <v>69</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>56</v>
@@ -3335,22 +3346,22 @@
         <v>64</v>
       </c>
       <c r="N43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P43" t="s">
         <v>62</v>
       </c>
       <c r="Q43" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R43" t="s">
         <v>64</v>
       </c>
       <c r="S43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U43" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
@@ -3358,7 +3369,7 @@
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -3370,7 +3381,7 @@
         <v>69</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>56</v>
@@ -3388,13 +3399,13 @@
         <v>64</v>
       </c>
       <c r="N44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P44" t="s">
         <v>62</v>
       </c>
       <c r="Q44" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="R44" t="s">
         <v>64</v>
@@ -3405,19 +3416,19 @@
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>56</v>
@@ -3429,13 +3440,13 @@
         <v>58</v>
       </c>
       <c r="L45" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M45" t="s">
         <v>64</v>
       </c>
       <c r="N45" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="P45" t="s">
         <v>62</v>
@@ -3446,40 +3457,40 @@
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E46" t="s">
         <v>54</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K46" t="s">
         <v>58</v>
       </c>
       <c r="L46" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s">
         <v>64</v>
       </c>
       <c r="N46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q46" t="s">
         <v>63</v>
@@ -3488,7 +3499,7 @@
         <v>64</v>
       </c>
       <c r="S46" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U46" t="s">
         <v>62</v>
@@ -3508,25 +3519,25 @@
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E47" t="s">
         <v>54</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J47" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K47" t="s">
         <v>58</v>
@@ -3538,19 +3549,19 @@
         <v>64</v>
       </c>
       <c r="N47" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P47" t="s">
         <v>62</v>
       </c>
       <c r="Q47" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R47" t="s">
         <v>64</v>
       </c>
       <c r="U47" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -3558,7 +3569,7 @@
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3567,10 +3578,10 @@
         <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>211</v>
+        <v>85</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>56</v>
@@ -3588,13 +3599,13 @@
         <v>64</v>
       </c>
       <c r="N48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P48" t="s">
         <v>62</v>
       </c>
       <c r="Q48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R48" t="s">
         <v>64</v>
@@ -3606,7 +3617,7 @@
         <v>62</v>
       </c>
       <c r="V48" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="W48" t="s">
         <v>64</v>
@@ -3617,19 +3628,19 @@
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" t="s">
         <v>69</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>56</v>
@@ -3641,7 +3652,7 @@
         <v>58</v>
       </c>
       <c r="L49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M49" t="s">
         <v>64</v>
@@ -3661,19 +3672,19 @@
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>217</v>
+      <c r="F50" s="7" t="s">
+        <v>249</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>56</v>
@@ -3685,13 +3696,13 @@
         <v>58</v>
       </c>
       <c r="L50" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M50" t="s">
         <v>64</v>
       </c>
       <c r="N50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P50" t="s">
         <v>62</v>
@@ -3708,25 +3719,25 @@
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E51" t="s">
         <v>54</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J51" t="s">
+        <v>62</v>
+      </c>
+      <c r="K51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" t="s">
         <v>219</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J51" t="s">
-        <v>62</v>
-      </c>
-      <c r="K51" t="s">
-        <v>58</v>
-      </c>
-      <c r="L51" t="s">
-        <v>220</v>
       </c>
       <c r="M51" t="s">
         <v>64</v>
@@ -3740,46 +3751,46 @@
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J52" t="s">
+        <v>62</v>
+      </c>
+      <c r="K52" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" t="s">
+        <v>79</v>
+      </c>
+      <c r="M52" t="s">
+        <v>64</v>
+      </c>
+      <c r="P52" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>221</v>
+      </c>
+      <c r="R52" t="s">
+        <v>64</v>
+      </c>
+      <c r="S52" t="s">
         <v>222</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J52" t="s">
-        <v>62</v>
-      </c>
-      <c r="K52" t="s">
-        <v>58</v>
-      </c>
-      <c r="L52" t="s">
-        <v>80</v>
-      </c>
-      <c r="M52" t="s">
-        <v>64</v>
-      </c>
-      <c r="P52" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>223</v>
-      </c>
-      <c r="R52" t="s">
-        <v>64</v>
-      </c>
-      <c r="S52" t="s">
-        <v>224</v>
       </c>
       <c r="T52" t="s">
         <v>116</v>
@@ -3788,19 +3799,19 @@
         <v>62</v>
       </c>
       <c r="V52" t="s">
+        <v>221</v>
+      </c>
+      <c r="W52" t="s">
+        <v>64</v>
+      </c>
+      <c r="X52" t="s">
         <v>223</v>
-      </c>
-      <c r="W52" t="s">
-        <v>64</v>
-      </c>
-      <c r="X52" t="s">
-        <v>225</v>
       </c>
       <c r="Y52" t="s">
         <v>72</v>
       </c>
       <c r="Z52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -3808,19 +3819,19 @@
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>54</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>56</v>
@@ -3832,16 +3843,16 @@
         <v>58</v>
       </c>
       <c r="L53" t="s">
+        <v>79</v>
+      </c>
+      <c r="M53" t="s">
+        <v>64</v>
+      </c>
+      <c r="P53" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q53" t="s">
         <v>80</v>
-      </c>
-      <c r="M53" t="s">
-        <v>64</v>
-      </c>
-      <c r="P53" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>81</v>
       </c>
       <c r="R53" t="s">
         <v>64</v>
@@ -3850,7 +3861,7 @@
         <v>72</v>
       </c>
       <c r="U53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
@@ -3858,19 +3869,19 @@
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E54" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>229</v>
+      <c r="F54" s="7" t="s">
+        <v>227</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>56</v>
@@ -3882,7 +3893,7 @@
         <v>58</v>
       </c>
       <c r="L54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M54" t="s">
         <v>64</v>
@@ -3891,13 +3902,13 @@
         <v>62</v>
       </c>
       <c r="Q54" t="s">
+        <v>221</v>
+      </c>
+      <c r="R54" t="s">
+        <v>64</v>
+      </c>
+      <c r="S54" t="s">
         <v>223</v>
-      </c>
-      <c r="R54" t="s">
-        <v>64</v>
-      </c>
-      <c r="S54" t="s">
-        <v>225</v>
       </c>
       <c r="T54" t="s">
         <v>116</v>
@@ -3915,7 +3926,7 @@
         <v>116</v>
       </c>
       <c r="Z54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
@@ -3923,40 +3934,40 @@
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E55" t="s">
         <v>54</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J55" t="s">
+        <v>62</v>
+      </c>
+      <c r="K55" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" t="s">
+        <v>230</v>
+      </c>
+      <c r="M55" t="s">
+        <v>64</v>
+      </c>
+      <c r="N55" t="s">
+        <v>58</v>
+      </c>
+      <c r="O55" t="s">
         <v>231</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J55" t="s">
-        <v>62</v>
-      </c>
-      <c r="K55" t="s">
-        <v>58</v>
-      </c>
-      <c r="L55" t="s">
-        <v>232</v>
-      </c>
-      <c r="M55" t="s">
-        <v>64</v>
-      </c>
-      <c r="N55" t="s">
-        <v>58</v>
-      </c>
-      <c r="O55" t="s">
-        <v>233</v>
       </c>
       <c r="P55" t="s">
         <v>62</v>
@@ -3967,7 +3978,7 @@
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C56">
         <v>3</v>
@@ -3978,8 +3989,8 @@
       <c r="E56" t="s">
         <v>69</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>235</v>
+      <c r="F56" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>56</v>
@@ -3997,13 +4008,13 @@
         <v>64</v>
       </c>
       <c r="N56" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P56" t="s">
         <v>62</v>
       </c>
       <c r="Q56" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="R56" t="s">
         <v>64</v>
@@ -4014,51 +4025,39 @@
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J57" t="s">
+        <v>62</v>
+      </c>
+      <c r="K57" t="s">
+        <v>58</v>
+      </c>
+      <c r="L57" t="s">
         <v>237</v>
       </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" t="s">
-        <v>54</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J57" t="s">
-        <v>62</v>
-      </c>
-      <c r="K57" t="s">
-        <v>58</v>
-      </c>
-      <c r="L57" t="s">
-        <v>80</v>
-      </c>
       <c r="M57" t="s">
         <v>64</v>
       </c>
       <c r="N57" t="s">
-        <v>239</v>
+        <v>61</v>
       </c>
       <c r="P57" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>240</v>
-      </c>
-      <c r="R57" t="s">
-        <v>64</v>
-      </c>
-      <c r="S57" t="s">
-        <v>72</v>
-      </c>
-      <c r="U57" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4067,19 +4066,19 @@
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E58" t="s">
         <v>54</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>56</v>
@@ -4091,7 +4090,7 @@
         <v>58</v>
       </c>
       <c r="L58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M58" t="s">
         <v>64</v>
@@ -4103,13 +4102,13 @@
         <v>59</v>
       </c>
       <c r="R58" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="S58" t="s">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="U58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
@@ -4117,19 +4116,19 @@
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E59" t="s">
         <v>69</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>56</v>
@@ -4141,7 +4140,7 @@
         <v>58</v>
       </c>
       <c r="L59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M59" t="s">
         <v>64</v>
@@ -4150,7 +4149,7 @@
         <v>62</v>
       </c>
       <c r="Q59" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="R59" t="s">
         <v>64</v>
@@ -4161,19 +4160,19 @@
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E60" t="s">
         <v>54</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>56</v>
@@ -4185,7 +4184,7 @@
         <v>58</v>
       </c>
       <c r="L60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M60" t="s">
         <v>64</v>
@@ -4206,7 +4205,7 @@
         <v>62</v>
       </c>
       <c r="V60" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="W60" t="s">
         <v>64</v>
@@ -4223,31 +4222,31 @@
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E61" t="s">
         <v>54</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>56</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="K61" t="s">
         <v>58</v>
       </c>
       <c r="L61" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="M61" t="s">
         <v>64</v>
@@ -4256,13 +4255,13 @@
         <v>62</v>
       </c>
       <c r="Q61" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="R61" t="s">
         <v>64</v>
       </c>
       <c r="S61" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="U61" t="s">
         <v>62</v>

--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0662DE-53CB-4398-A64A-FAB773146A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92590A6F-89AF-4B7B-A6C2-661E3F18A1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="239">
   <si>
     <t>CardId</t>
   </si>
@@ -101,51 +101,6 @@
   </si>
   <si>
     <t>Effect3_Condition</t>
-  </si>
-  <si>
-    <t>Effect4_Type</t>
-  </si>
-  <si>
-    <t>Effect4_Target</t>
-  </si>
-  <si>
-    <t>Effect4_Param1</t>
-  </si>
-  <si>
-    <t>Effect4_Param2</t>
-  </si>
-  <si>
-    <t>Effect4_Condition</t>
-  </si>
-  <si>
-    <t>Effect5_Type</t>
-  </si>
-  <si>
-    <t>Effect5_Target</t>
-  </si>
-  <si>
-    <t>Effect5_Param1</t>
-  </si>
-  <si>
-    <t>Effect5_Param2</t>
-  </si>
-  <si>
-    <t>Effect5_Condition</t>
-  </si>
-  <si>
-    <t>Effect6_Type</t>
-  </si>
-  <si>
-    <t>Effect6_Target</t>
-  </si>
-  <si>
-    <t>Effect6_Param1</t>
-  </si>
-  <si>
-    <t>Effect6_Param2</t>
-  </si>
-  <si>
-    <t>Effect6_Condition</t>
   </si>
   <si>
     <t>int</t>
@@ -274,6 +229,9 @@
     <t>穿云</t>
   </si>
   <si>
+    <t>【御剑】并对目标位置造成6点伤害\n【链接】，【穿透】则获得1点能量</t>
+  </si>
+  <si>
     <t>LinkSwords</t>
   </si>
   <si>
@@ -358,13 +316,16 @@
     <t>剑来</t>
   </si>
   <si>
+    <t>【剑来】</t>
+  </si>
+  <si>
     <t>RecallSwords</t>
   </si>
   <si>
     <t>并锋</t>
   </si>
   <si>
-    <t>获得1点能量，人剑合一再获得1点能量</t>
+    <t>获得1点能量\n人剑合一再获得1点能量</t>
   </si>
   <si>
     <t>ManSwordUnity</t>
@@ -424,7 +385,7 @@
     <t>遁影</t>
   </si>
   <si>
-    <t>【遁形】1距离\n如果【易位】【剑来】</t>
+    <t>【遁形】1距离\n如果【易位】，【剑来】</t>
   </si>
   <si>
     <t>RecallToSlot</t>
@@ -673,7 +634,7 @@
     <t>灵潮</t>
   </si>
   <si>
-    <t>每回合开始随机位置生成【灵剑】\n【灵剑】途经伤害+4\n【消耗】</t>
+    <t>【灵剑】途经伤害+4\n每回合开始随机位置生成【灵剑】\n【消耗】</t>
   </si>
   <si>
     <t>HasTurnStartSpiritSpawn</t>
@@ -691,15 +652,24 @@
     <t>牵络</t>
   </si>
   <si>
+    <t>【链接】\n本次【链接】施加12点【护甲】</t>
+  </si>
+  <si>
     <t>贯脉</t>
   </si>
   <si>
+    <t>【链接】\n【穿透】则再次【链接】</t>
+  </si>
+  <si>
     <t>LinkSwordsRepeat</t>
   </si>
   <si>
     <t>缠丝</t>
   </si>
   <si>
+    <t>【链接】\n对【链接】的敌人施加2层【虚弱】，【穿透】则再施加1层【易伤】</t>
+  </si>
+  <si>
     <t>LinkDebuff</t>
   </si>
   <si>
@@ -727,80 +697,61 @@
     <t>【链接】\n【消耗】所有【护甲】，对全体敌人造成等量伤害\n【穿透】则恢复一半【护甲】</t>
   </si>
   <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>北斗</t>
+  </si>
+  <si>
+    <t>【链接】均视为【穿透】\n【消耗】</t>
+  </si>
+  <si>
+    <t>LinkAlwaysPenetrate</t>
+  </si>
+  <si>
+    <t>织网</t>
+  </si>
+  <si>
+    <t>【链接】\n尝试在每个位置生成灵剑，每把灵剑消耗6护甲\n优先在敌人位置生成</t>
+  </si>
+  <si>
+    <t>SpawnSpiritsByArmor</t>
+  </si>
+  <si>
+    <t>初照</t>
+  </si>
+  <si>
+    <t>【链接】\n【穿透】则全体造成4点伤害</t>
+  </si>
+  <si>
+    <t>AllEnemies</t>
+  </si>
+  <si>
+    <t>离身</t>
+  </si>
+  <si>
+    <t>【链接】\n随机去除1个负面效果</t>
+  </si>
+  <si>
+    <t>PurgeRandomDebuff</t>
+  </si>
+  <si>
+    <t>连丝</t>
+  </si>
+  <si>
+    <t>【链接】\n抽1张牌，弃1张手牌</t>
+  </si>
+  <si>
+    <t>凝雪</t>
+  </si>
+  <si>
+    <t>在指定位置生成【灵剑】\n对所有【灵剑】的位置的敌人造成7点伤害</t>
+  </si>
+  <si>
+    <t>SpiritPositionsDamage</t>
+  </si>
+  <si>
     <t>LinkSacrificeBlock</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>北斗</t>
-  </si>
-  <si>
-    <t>【链接】均视为【穿透】\n【消耗】</t>
-  </si>
-  <si>
-    <t>LinkAlwaysPenetrate</t>
-  </si>
-  <si>
-    <t>织网</t>
-  </si>
-  <si>
-    <t>【链接】\n尝试在每个位置生成灵剑，每把灵剑消耗6护甲\n优先在敌人位置生成</t>
-  </si>
-  <si>
-    <t>SpawnSpiritsByArmor</t>
-  </si>
-  <si>
-    <t>初照</t>
-  </si>
-  <si>
-    <t>【链接】\n【穿透】则全体造成4点伤害</t>
-  </si>
-  <si>
-    <t>AllEnemies</t>
-  </si>
-  <si>
-    <t>离身</t>
-  </si>
-  <si>
-    <t>【链接】\n随机去除1个负面效果</t>
-  </si>
-  <si>
-    <t>PurgeRandomDebuff</t>
-  </si>
-  <si>
-    <t>连丝</t>
-  </si>
-  <si>
-    <t>【链接】\n抽1张牌，弃1张手牌</t>
-  </si>
-  <si>
-    <t>凝雪</t>
-  </si>
-  <si>
-    <t>在指定位置生成【灵剑】\n对所有【灵剑】的位置的敌人造成7点伤害</t>
-  </si>
-  <si>
-    <t>SpiritPositionsDamage</t>
-  </si>
-  <si>
-    <t>【链接】\n本次【链接】施加12点【护甲】</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>【链接】\n【穿透】则再次【链接】</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>【链接】\n对【链接】的敌人施加2层【虚弱】，【穿透】则再施加1层【易伤】</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>【剑来】</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>【御剑】并对目标位置造成6点伤害\n【链接】，【穿透】则获得1点能量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1155,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:Z61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -1167,9 +1118,23 @@
     <col min="7" max="7" width="18.33203125" style="4" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="22.21875" customWidth="1"/>
+    <col min="13" max="13" width="14.21875" customWidth="1"/>
+    <col min="14" max="14" width="22.21875" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" customWidth="1"/>
+    <col min="16" max="16" width="17.77734375" customWidth="1"/>
+    <col min="17" max="17" width="21.77734375" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" customWidth="1"/>
+    <col min="19" max="19" width="20.109375" customWidth="1"/>
+    <col min="21" max="21" width="17.77734375" customWidth="1"/>
+    <col min="22" max="22" width="15.5546875" customWidth="1"/>
+    <col min="24" max="24" width="11.109375" customWidth="1"/>
+    <col min="26" max="26" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1248,830 +1213,740 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+    </row>
+    <row r="2" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="B3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="F3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="G3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="I3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" s="1" customFormat="1" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N4" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q4" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="R4" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S4" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="U4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>12002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
         <v>56</v>
       </c>
-      <c r="J6" t="s">
-        <v>62</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" t="s">
         <v>58</v>
       </c>
-      <c r="L6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>73</v>
-      </c>
       <c r="R6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="M7" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>12004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>253</v>
+        <v>64</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" t="s">
+        <v>66</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" t="s">
         <v>57</v>
       </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M8" t="s">
-        <v>60</v>
-      </c>
-      <c r="N8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>79</v>
-      </c>
-      <c r="R8" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" t="s">
-        <v>62</v>
-      </c>
-      <c r="V8" t="s">
-        <v>80</v>
-      </c>
-      <c r="W8" t="s">
-        <v>64</v>
-      </c>
-      <c r="X8" t="s">
-        <v>72</v>
-      </c>
       <c r="Z8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" t="s">
         <v>56</v>
       </c>
-      <c r="J9" t="s">
+      <c r="R9" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" t="s">
         <v>57</v>
       </c>
-      <c r="K9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" t="s">
-        <v>79</v>
-      </c>
-      <c r="M9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" t="s">
-        <v>64</v>
-      </c>
-      <c r="S9" t="s">
-        <v>72</v>
-      </c>
       <c r="U9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10" t="s">
         <v>57</v>
       </c>
-      <c r="K10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" t="s">
-        <v>72</v>
-      </c>
       <c r="P10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="Q10" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="R10" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="V10" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="W10" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>12007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="P11" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="R11" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S11" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="U11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K12" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L12" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M12" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P12" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q12" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="R12" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="S12" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="U12" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="V12" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="W12" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K13" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M13" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="P13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>252</v>
+        <v>93</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J14" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K15" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N15" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="R15" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S15" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>12011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L16" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N16" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -2079,40 +1954,40 @@
         <v>12012</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J17" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" t="s">
         <v>103</v>
       </c>
-      <c r="K17" t="s">
-        <v>116</v>
-      </c>
       <c r="L17" t="s">
+        <v>90</v>
+      </c>
+      <c r="M17" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" t="s">
         <v>104</v>
       </c>
-      <c r="M17" t="s">
-        <v>64</v>
-      </c>
-      <c r="N17" t="s">
-        <v>117</v>
-      </c>
       <c r="P17" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
@@ -2120,49 +1995,49 @@
         <v>12013</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L18" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="M18" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P18" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="R18" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S18" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="U18" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
@@ -2170,46 +2045,46 @@
         <v>12014</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K19" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N19" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q19" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="R19" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
@@ -2217,46 +2092,46 @@
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K20" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="M20" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N20" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="P20" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q20" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="R20" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
@@ -2264,46 +2139,46 @@
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L21" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="M21" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="Q21" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="R21" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U21" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
@@ -2311,61 +2186,61 @@
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" t="s">
         <v>56</v>
       </c>
-      <c r="J22" t="s">
-        <v>62</v>
-      </c>
-      <c r="K22" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" t="s">
-        <v>71</v>
-      </c>
       <c r="M22" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N22" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P22" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q22" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="R22" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S22" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U22" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="V22" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="W22" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z22" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
@@ -2373,46 +2248,46 @@
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" t="s">
+        <v>47</v>
+      </c>
+      <c r="K23" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" t="s">
         <v>56</v>
       </c>
-      <c r="J23" t="s">
-        <v>62</v>
-      </c>
-      <c r="K23" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" t="s">
-        <v>71</v>
-      </c>
       <c r="M23" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N23" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P23" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="Q23" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="R23" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
@@ -2420,61 +2295,61 @@
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K24" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L24" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="M24" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N24" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="P24" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="Q24" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="R24" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S24" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U24" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="V24" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="W24" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z24" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
@@ -2482,49 +2357,49 @@
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="L25" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N25" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="P25" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="Q25" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="R25" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U25" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
@@ -2532,61 +2407,61 @@
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J26" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="M26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N26" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="Q26" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="R26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S26" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="U26" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="V26" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="W26" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z26" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
@@ -2594,37 +2469,37 @@
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J27" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K27" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P27" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
@@ -2632,34 +2507,34 @@
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J28" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K28" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L28" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="M28" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
@@ -2667,49 +2542,49 @@
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J29" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L29" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="M29" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P29" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q29" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="R29" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S29" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U29" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -2717,61 +2592,61 @@
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" t="s">
+        <v>47</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" t="s">
+        <v>144</v>
+      </c>
+      <c r="M30" t="s">
+        <v>49</v>
+      </c>
+      <c r="P30" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q30" t="s">
         <v>56</v>
       </c>
-      <c r="J30" t="s">
-        <v>62</v>
-      </c>
-      <c r="K30" t="s">
-        <v>58</v>
-      </c>
-      <c r="L30" t="s">
-        <v>157</v>
-      </c>
-      <c r="M30" t="s">
-        <v>64</v>
-      </c>
-      <c r="P30" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>71</v>
-      </c>
       <c r="R30" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S30" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U30" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V30" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="W30" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="X30" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="Z30" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
@@ -2779,52 +2654,52 @@
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J31" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K31" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L31" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="M31" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P31" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q31" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="R31" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U31" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V31" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="W31" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
@@ -2832,52 +2707,52 @@
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J32" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K32" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L32" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="M32" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P32" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q32" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="R32" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U32" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V32" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="W32" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
@@ -2885,43 +2760,43 @@
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C33">
         <v>-1</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J33" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K33" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L33" t="s">
+        <v>144</v>
+      </c>
+      <c r="M33" t="s">
+        <v>49</v>
+      </c>
+      <c r="P33" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q33" t="s">
         <v>157</v>
       </c>
-      <c r="M33" t="s">
-        <v>64</v>
-      </c>
-      <c r="P33" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>170</v>
-      </c>
       <c r="R33" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -2929,43 +2804,43 @@
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K34" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L34" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="M34" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P34" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q34" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="R34" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
@@ -2973,40 +2848,40 @@
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J35" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M35" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N35" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="P35" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
@@ -3014,46 +2889,46 @@
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J36" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L36" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M36" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N36" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="P36" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q36" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="R36" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
@@ -3061,34 +2936,34 @@
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J37" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K37" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L37" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="M37" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
@@ -3096,40 +2971,40 @@
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J38" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" t="s">
+        <v>144</v>
+      </c>
+      <c r="M38" t="s">
+        <v>49</v>
+      </c>
+      <c r="N38" t="s">
         <v>62</v>
       </c>
-      <c r="K38" t="s">
-        <v>58</v>
-      </c>
-      <c r="L38" t="s">
-        <v>157</v>
-      </c>
-      <c r="M38" t="s">
-        <v>64</v>
-      </c>
-      <c r="N38" t="s">
-        <v>77</v>
-      </c>
       <c r="P38" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
@@ -3137,46 +3012,46 @@
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J39" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" t="s">
+        <v>45</v>
+      </c>
+      <c r="N39" t="s">
         <v>62</v>
       </c>
-      <c r="K39" t="s">
-        <v>58</v>
-      </c>
-      <c r="L39" t="s">
-        <v>59</v>
-      </c>
-      <c r="M39" t="s">
-        <v>60</v>
-      </c>
-      <c r="N39" t="s">
-        <v>77</v>
-      </c>
       <c r="P39" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q39" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="R39" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
@@ -3184,34 +3059,34 @@
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J40" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K40" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L40" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="M40" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -3219,49 +3094,49 @@
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E41" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J41" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K41" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L41" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="M41" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N41" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="P41" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q41" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="R41" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U41" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
@@ -3269,46 +3144,46 @@
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J42" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K42" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L42" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M42" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N42" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="P42" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="R42" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
@@ -3316,52 +3191,52 @@
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J43" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K43" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L43" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M43" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N43" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="P43" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q43" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="R43" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S43" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="U43" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
@@ -3369,46 +3244,46 @@
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J44" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K44" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L44" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M44" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N44" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="P44" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q44" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="R44" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
@@ -3416,40 +3291,40 @@
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J45" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K45" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L45" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="M45" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N45" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="P45" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
@@ -3457,61 +3332,61 @@
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E46" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J46" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K46" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L46" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M46" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N46" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="Q46" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="R46" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S46" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="U46" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V46" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="W46" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="Z46" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -3519,49 +3394,49 @@
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E47" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J47" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K47" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L47" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M47" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N47" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="P47" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q47" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="R47" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="U47" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -3569,58 +3444,58 @@
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" t="s">
+        <v>43</v>
+      </c>
+      <c r="L48" t="s">
+        <v>48</v>
+      </c>
+      <c r="M48" t="s">
+        <v>49</v>
+      </c>
+      <c r="N48" t="s">
+        <v>200</v>
+      </c>
+      <c r="P48" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>112</v>
+      </c>
+      <c r="R48" t="s">
+        <v>49</v>
+      </c>
+      <c r="S48" t="s">
         <v>62</v>
       </c>
-      <c r="K48" t="s">
-        <v>58</v>
-      </c>
-      <c r="L48" t="s">
-        <v>63</v>
-      </c>
-      <c r="M48" t="s">
-        <v>64</v>
-      </c>
-      <c r="N48" t="s">
-        <v>213</v>
-      </c>
-      <c r="P48" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>125</v>
-      </c>
-      <c r="R48" t="s">
-        <v>64</v>
-      </c>
-      <c r="S48" t="s">
-        <v>77</v>
-      </c>
       <c r="U48" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V48" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="W48" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
@@ -3628,43 +3503,43 @@
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J49" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="K49" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L49" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="M49" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P49" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q49" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="R49" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
@@ -3672,40 +3547,40 @@
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J50" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K50" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L50" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M50" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N50" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="P50" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
@@ -3713,37 +3588,37 @@
         <v>12046</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E51" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J51" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K51" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L51" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M51" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P51" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
@@ -3751,67 +3626,67 @@
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J52" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K52" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L52" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M52" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P52" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q52" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="R52" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S52" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="T52" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="U52" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V52" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="W52" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="X52" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="Y52" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="Z52" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -3819,49 +3694,49 @@
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E53" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J53" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K53" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L53" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M53" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P53" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q53" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="R53" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S53" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U53" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
@@ -3869,64 +3744,64 @@
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E54" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="G54" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J54" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" t="s">
+        <v>43</v>
+      </c>
+      <c r="L54" t="s">
+        <v>65</v>
+      </c>
+      <c r="M54" t="s">
+        <v>49</v>
+      </c>
+      <c r="P54" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>211</v>
+      </c>
+      <c r="R54" t="s">
+        <v>49</v>
+      </c>
+      <c r="S54" t="s">
+        <v>213</v>
+      </c>
+      <c r="T54" t="s">
+        <v>103</v>
+      </c>
+      <c r="U54" t="s">
+        <v>47</v>
+      </c>
+      <c r="V54" t="s">
         <v>56</v>
       </c>
-      <c r="J54" t="s">
-        <v>62</v>
-      </c>
-      <c r="K54" t="s">
-        <v>58</v>
-      </c>
-      <c r="L54" t="s">
-        <v>79</v>
-      </c>
-      <c r="M54" t="s">
-        <v>64</v>
-      </c>
-      <c r="P54" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>221</v>
-      </c>
-      <c r="R54" t="s">
-        <v>64</v>
-      </c>
-      <c r="S54" t="s">
-        <v>223</v>
-      </c>
-      <c r="T54" t="s">
-        <v>116</v>
-      </c>
-      <c r="U54" t="s">
-        <v>62</v>
-      </c>
-      <c r="V54" t="s">
-        <v>71</v>
-      </c>
       <c r="W54" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="X54" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Z54" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
@@ -3934,43 +3809,43 @@
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E55" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J55" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K55" t="s">
-        <v>58</v>
-      </c>
-      <c r="L55" t="s">
-        <v>230</v>
+        <v>43</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="M55" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N55" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="O55" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="P55" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
@@ -3978,46 +3853,46 @@
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="E56" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J56" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K56" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L56" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M56" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N56" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="P56" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q56" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="R56" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
@@ -4025,40 +3900,40 @@
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J57" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K57" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L57" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M57" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="N57" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="P57" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
@@ -4066,49 +3941,49 @@
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E58" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J58" t="s">
+        <v>47</v>
+      </c>
+      <c r="K58" t="s">
+        <v>43</v>
+      </c>
+      <c r="L58" t="s">
+        <v>65</v>
+      </c>
+      <c r="M58" t="s">
+        <v>49</v>
+      </c>
+      <c r="P58" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>44</v>
+      </c>
+      <c r="R58" t="s">
+        <v>229</v>
+      </c>
+      <c r="S58" t="s">
         <v>62</v>
       </c>
-      <c r="K58" t="s">
-        <v>58</v>
-      </c>
-      <c r="L58" t="s">
-        <v>79</v>
-      </c>
-      <c r="M58" t="s">
-        <v>64</v>
-      </c>
-      <c r="P58" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>59</v>
-      </c>
-      <c r="R58" t="s">
-        <v>240</v>
-      </c>
-      <c r="S58" t="s">
-        <v>77</v>
-      </c>
       <c r="U58" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
@@ -4116,43 +3991,43 @@
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E59" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J59" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K59" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L59" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M59" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P59" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q59" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="R59" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
@@ -4160,61 +4035,61 @@
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G60" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J60" t="s">
+        <v>47</v>
+      </c>
+      <c r="K60" t="s">
+        <v>43</v>
+      </c>
+      <c r="L60" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" t="s">
+        <v>49</v>
+      </c>
+      <c r="P60" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q60" t="s">
         <v>56</v>
       </c>
-      <c r="J60" t="s">
-        <v>62</v>
-      </c>
-      <c r="K60" t="s">
-        <v>58</v>
-      </c>
-      <c r="L60" t="s">
-        <v>79</v>
-      </c>
-      <c r="M60" t="s">
-        <v>64</v>
-      </c>
-      <c r="P60" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>71</v>
-      </c>
       <c r="R60" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S60" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="U60" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="V60" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="W60" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="X60" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="Z60" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
@@ -4222,49 +4097,49 @@
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E61" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="J61" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="K61" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L61" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M61" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="P61" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="Q61" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="R61" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="S61" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="U61" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
+++ b/Assets/GameResource/Excel/卡牌配置-基础数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\LastGame\Assets\GameResource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92590A6F-89AF-4B7B-A6C2-661E3F18A1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20559658-65CE-424D-B703-68205DE493C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="672" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,9 +160,6 @@
     <t>造成6点伤害\n【御剑】但不造成途经伤害</t>
   </si>
   <si>
-    <t>bear</t>
-  </si>
-  <si>
     <t>MoveSword</t>
   </si>
   <si>
@@ -753,6 +750,9 @@
   <si>
     <t>LinkSacrificeBlock</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bay</t>
   </si>
 </sst>
 </file>
@@ -1343,37 +1343,37 @@
         <v>40</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J4" t="s">
         <v>41</v>
       </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
       <c r="K4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L4" t="s">
         <v>43</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>44</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>45</v>
       </c>
-      <c r="N4" t="s">
-        <v>46</v>
-      </c>
       <c r="P4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" t="s">
-        <v>48</v>
-      </c>
       <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
         <v>49</v>
       </c>
-      <c r="S4" t="s">
-        <v>50</v>
-      </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -1381,7 +1381,7 @@
         <v>12001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1393,16 +1393,16 @@
         <v>39</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J5" t="s">
         <v>41</v>
       </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1410,7 +1410,7 @@
         <v>12002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1419,37 +1419,37 @@
         <v>38</v>
       </c>
       <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s">
         <v>56</v>
       </c>
-      <c r="M6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" t="s">
         <v>57</v>
       </c>
-      <c r="P6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>58</v>
-      </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -1457,7 +1457,7 @@
         <v>12003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>39</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s">
         <v>61</v>
       </c>
-      <c r="M7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" t="s">
-        <v>62</v>
-      </c>
       <c r="P7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -1498,7 +1498,7 @@
         <v>12004</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1507,52 +1507,52 @@
         <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>42</v>
-      </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" t="s">
         <v>65</v>
       </c>
-      <c r="R8" t="s">
-        <v>49</v>
-      </c>
-      <c r="U8" t="s">
-        <v>47</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" t="s">
         <v>66</v>
-      </c>
-      <c r="W8" t="s">
-        <v>49</v>
-      </c>
-      <c r="X8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -1560,7 +1560,7 @@
         <v>12005</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1572,37 +1572,37 @@
         <v>39</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" t="s">
         <v>41</v>
       </c>
-      <c r="J9" t="s">
-        <v>42</v>
-      </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" t="s">
         <v>56</v>
       </c>
-      <c r="R9" t="s">
-        <v>49</v>
-      </c>
-      <c r="S9" t="s">
-        <v>57</v>
-      </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -1610,7 +1610,7 @@
         <v>12006</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1619,49 +1619,49 @@
         <v>38</v>
       </c>
       <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+      <c r="P10" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>73</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
+        <v>48</v>
+      </c>
+      <c r="U10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" t="s">
         <v>74</v>
       </c>
-      <c r="R10" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" t="s">
-        <v>73</v>
-      </c>
-      <c r="V10" t="s">
-        <v>75</v>
-      </c>
       <c r="W10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -1669,52 +1669,52 @@
         <v>12007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="P11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q11" t="s">
         <v>79</v>
       </c>
-      <c r="P11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
+        <v>48</v>
+      </c>
+      <c r="S11" t="s">
         <v>80</v>
       </c>
-      <c r="R11" t="s">
-        <v>49</v>
-      </c>
-      <c r="S11" t="s">
-        <v>81</v>
-      </c>
       <c r="U11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -1722,7 +1722,7 @@
         <v>12008</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1731,52 +1731,52 @@
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="P12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="s">
         <v>43</v>
       </c>
-      <c r="L12" t="s">
+      <c r="R12" t="s">
         <v>44</v>
       </c>
-      <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="S12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>44</v>
-      </c>
-      <c r="R12" t="s">
-        <v>45</v>
-      </c>
-      <c r="S12" t="s">
-        <v>85</v>
-      </c>
       <c r="U12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
@@ -1784,40 +1784,40 @@
         <v>10002</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>39</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" t="s">
         <v>89</v>
       </c>
-      <c r="K13" t="s">
-        <v>57</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" t="s">
         <v>90</v>
       </c>
-      <c r="M13" t="s">
-        <v>49</v>
-      </c>
-      <c r="N13" t="s">
-        <v>91</v>
-      </c>
       <c r="P13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -1825,34 +1825,34 @@
         <v>12009</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
         <v>39</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" t="s">
-        <v>94</v>
-      </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
@@ -1860,52 +1860,52 @@
         <v>12010</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>39</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" t="s">
+        <v>56</v>
+      </c>
+      <c r="P15" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>65</v>
+      </c>
+      <c r="R15" t="s">
+        <v>48</v>
+      </c>
+      <c r="S15" t="s">
+        <v>56</v>
+      </c>
+      <c r="U15" t="s">
         <v>96</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" t="s">
-        <v>49</v>
-      </c>
-      <c r="N15" t="s">
-        <v>57</v>
-      </c>
-      <c r="P15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>66</v>
-      </c>
-      <c r="R15" t="s">
-        <v>49</v>
-      </c>
-      <c r="S15" t="s">
-        <v>57</v>
-      </c>
-      <c r="U15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -1913,40 +1913,40 @@
         <v>12011</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E16" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J16" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" t="s">
+        <v>90</v>
+      </c>
+      <c r="P16" t="s">
         <v>99</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J16" t="s">
-        <v>89</v>
-      </c>
-      <c r="K16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L16" t="s">
-        <v>90</v>
-      </c>
-      <c r="M16" t="s">
-        <v>49</v>
-      </c>
-      <c r="N16" t="s">
-        <v>91</v>
-      </c>
-      <c r="P16" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
@@ -1954,40 +1954,40 @@
         <v>12012</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>39</v>
       </c>
       <c r="F17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K17" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
         <v>89</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" t="s">
         <v>103</v>
       </c>
-      <c r="L17" t="s">
-        <v>90</v>
-      </c>
-      <c r="M17" t="s">
-        <v>49</v>
-      </c>
-      <c r="N17" t="s">
-        <v>104</v>
-      </c>
       <c r="P17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
@@ -1995,49 +1995,49 @@
         <v>12013</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
@@ -2045,46 +2045,46 @@
         <v>12014</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" t="s">
+        <v>89</v>
+      </c>
+      <c r="M19" t="s">
+        <v>48</v>
+      </c>
+      <c r="N19" t="s">
+        <v>84</v>
+      </c>
+      <c r="P19" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J19" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" t="s">
-        <v>90</v>
-      </c>
-      <c r="M19" t="s">
-        <v>49</v>
-      </c>
-      <c r="N19" t="s">
-        <v>85</v>
-      </c>
-      <c r="P19" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>109</v>
-      </c>
       <c r="R19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
@@ -2092,46 +2092,46 @@
         <v>12015</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" t="s">
-        <v>47</v>
-      </c>
-      <c r="K20" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
+        <v>48</v>
+      </c>
+      <c r="N20" t="s">
         <v>112</v>
       </c>
-      <c r="M20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="P20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q20" t="s">
         <v>113</v>
       </c>
-      <c r="P20" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>114</v>
-      </c>
       <c r="R20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
@@ -2139,46 +2139,46 @@
         <v>12016</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>39</v>
       </c>
       <c r="F21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J21" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" t="s">
-        <v>57</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
+        <v>48</v>
+      </c>
+      <c r="P21" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q21" t="s">
         <v>117</v>
       </c>
-      <c r="M21" t="s">
-        <v>49</v>
-      </c>
-      <c r="P21" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>118</v>
-      </c>
       <c r="R21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
@@ -2186,61 +2186,61 @@
         <v>12017</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" t="s">
+        <v>56</v>
+      </c>
+      <c r="P22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>65</v>
+      </c>
+      <c r="R22" t="s">
+        <v>48</v>
+      </c>
+      <c r="S22" t="s">
+        <v>56</v>
+      </c>
+      <c r="U22" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" t="s">
-        <v>47</v>
-      </c>
-      <c r="K22" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" t="s">
-        <v>49</v>
-      </c>
-      <c r="N22" t="s">
-        <v>57</v>
-      </c>
-      <c r="P22" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>66</v>
-      </c>
-      <c r="R22" t="s">
-        <v>49</v>
-      </c>
-      <c r="S22" t="s">
-        <v>57</v>
-      </c>
-      <c r="U22" t="s">
-        <v>121</v>
-      </c>
       <c r="V22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
@@ -2248,46 +2248,46 @@
         <v>12018</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>39</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N23" t="s">
         <v>56</v>
       </c>
-      <c r="M23" t="s">
-        <v>49</v>
-      </c>
-      <c r="N23" t="s">
-        <v>57</v>
-      </c>
       <c r="P23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
@@ -2295,61 +2295,61 @@
         <v>12019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s">
         <v>39</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" t="s">
+        <v>42</v>
+      </c>
+      <c r="L24" t="s">
         <v>125</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J24" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
+        <v>48</v>
+      </c>
+      <c r="N24" t="s">
+        <v>56</v>
+      </c>
+      <c r="P24" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q24" t="s">
         <v>126</v>
       </c>
-      <c r="M24" t="s">
-        <v>49</v>
-      </c>
-      <c r="N24" t="s">
-        <v>57</v>
-      </c>
-      <c r="P24" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>127</v>
-      </c>
       <c r="R24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
@@ -2357,49 +2357,49 @@
         <v>12020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
         <v>39</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J25" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" t="s">
+        <v>89</v>
+      </c>
+      <c r="M25" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" t="s">
         <v>129</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J25" t="s">
-        <v>89</v>
-      </c>
-      <c r="K25" t="s">
-        <v>57</v>
-      </c>
-      <c r="L25" t="s">
-        <v>90</v>
-      </c>
-      <c r="M25" t="s">
-        <v>49</v>
-      </c>
-      <c r="N25" t="s">
-        <v>130</v>
-      </c>
       <c r="P25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
@@ -2407,61 +2407,61 @@
         <v>12021</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J26" t="s">
+        <v>88</v>
+      </c>
+      <c r="K26" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" t="s">
+        <v>89</v>
+      </c>
+      <c r="M26" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" t="s">
+      <c r="P26" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q26" t="s">
         <v>89</v>
       </c>
-      <c r="K26" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M26" t="s">
-        <v>49</v>
-      </c>
-      <c r="N26" t="s">
-        <v>133</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
+        <v>48</v>
+      </c>
+      <c r="S26" t="s">
         <v>134</v>
       </c>
-      <c r="Q26" t="s">
-        <v>90</v>
-      </c>
-      <c r="R26" t="s">
-        <v>49</v>
-      </c>
-      <c r="S26" t="s">
-        <v>135</v>
-      </c>
       <c r="U26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
@@ -2469,37 +2469,37 @@
         <v>12022</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F27" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J27" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" t="s">
-        <v>138</v>
-      </c>
       <c r="M27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
@@ -2507,34 +2507,34 @@
         <v>12023</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J28" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L28" t="s">
         <v>140</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J28" t="s">
-        <v>47</v>
-      </c>
-      <c r="K28" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" t="s">
-        <v>141</v>
-      </c>
       <c r="M28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
@@ -2542,7 +2542,7 @@
         <v>12024</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -2554,37 +2554,37 @@
         <v>39</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J29" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" t="s">
+        <v>42</v>
+      </c>
+      <c r="L29" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J29" t="s">
-        <v>47</v>
-      </c>
-      <c r="K29" t="s">
-        <v>43</v>
-      </c>
-      <c r="L29" t="s">
-        <v>144</v>
-      </c>
       <c r="M29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
@@ -2592,7 +2592,7 @@
         <v>12025</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2604,49 +2604,49 @@
         <v>39</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J30" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30" t="s">
+        <v>143</v>
+      </c>
+      <c r="M30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>55</v>
+      </c>
+      <c r="R30" t="s">
+        <v>48</v>
+      </c>
+      <c r="S30" t="s">
+        <v>56</v>
+      </c>
+      <c r="U30" t="s">
+        <v>46</v>
+      </c>
+      <c r="V30" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" t="s">
-        <v>47</v>
-      </c>
-      <c r="K30" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" t="s">
-        <v>144</v>
-      </c>
-      <c r="M30" t="s">
-        <v>49</v>
-      </c>
-      <c r="P30" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q30" t="s">
+      <c r="W30" t="s">
+        <v>48</v>
+      </c>
+      <c r="X30" t="s">
         <v>56</v>
       </c>
-      <c r="R30" t="s">
-        <v>49</v>
-      </c>
-      <c r="S30" t="s">
-        <v>57</v>
-      </c>
-      <c r="U30" t="s">
-        <v>47</v>
-      </c>
-      <c r="V30" t="s">
-        <v>147</v>
-      </c>
-      <c r="W30" t="s">
-        <v>49</v>
-      </c>
-      <c r="X30" t="s">
-        <v>57</v>
-      </c>
       <c r="Z30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
@@ -2654,7 +2654,7 @@
         <v>12026</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -2663,43 +2663,43 @@
         <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J31" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" t="s">
+        <v>42</v>
+      </c>
+      <c r="L31" t="s">
+        <v>143</v>
+      </c>
+      <c r="M31" t="s">
+        <v>48</v>
+      </c>
+      <c r="P31" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>93</v>
+      </c>
+      <c r="R31" t="s">
+        <v>48</v>
+      </c>
+      <c r="U31" t="s">
+        <v>46</v>
+      </c>
+      <c r="V31" t="s">
         <v>149</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" t="s">
-        <v>47</v>
-      </c>
-      <c r="K31" t="s">
-        <v>43</v>
-      </c>
-      <c r="L31" t="s">
-        <v>144</v>
-      </c>
-      <c r="M31" t="s">
-        <v>49</v>
-      </c>
-      <c r="P31" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>94</v>
-      </c>
-      <c r="R31" t="s">
-        <v>49</v>
-      </c>
-      <c r="U31" t="s">
-        <v>47</v>
-      </c>
-      <c r="V31" t="s">
-        <v>150</v>
-      </c>
       <c r="W31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
@@ -2707,52 +2707,52 @@
         <v>12027</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F32" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J32" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" t="s">
+        <v>42</v>
+      </c>
+      <c r="L32" t="s">
         <v>152</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" t="s">
-        <v>47</v>
-      </c>
-      <c r="K32" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="M32" t="s">
+        <v>48</v>
+      </c>
+      <c r="P32" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q32" t="s">
         <v>153</v>
       </c>
-      <c r="M32" t="s">
-        <v>49</v>
-      </c>
-      <c r="P32" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>154</v>
-      </c>
       <c r="R32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
@@ -2760,7 +2760,7 @@
         <v>12028</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33">
         <v>-1</v>
@@ -2769,34 +2769,34 @@
         <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" t="s">
+        <v>46</v>
+      </c>
+      <c r="K33" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M33" t="s">
+        <v>48</v>
+      </c>
+      <c r="P33" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q33" t="s">
         <v>156</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J33" t="s">
-        <v>47</v>
-      </c>
-      <c r="K33" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" t="s">
-        <v>144</v>
-      </c>
-      <c r="M33" t="s">
-        <v>49</v>
-      </c>
-      <c r="P33" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>157</v>
-      </c>
       <c r="R33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
@@ -2804,7 +2804,7 @@
         <v>12029</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2813,34 +2813,34 @@
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J34" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" t="s">
+        <v>42</v>
+      </c>
+      <c r="L34" t="s">
         <v>159</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J34" t="s">
-        <v>47</v>
-      </c>
-      <c r="K34" t="s">
-        <v>43</v>
-      </c>
-      <c r="L34" t="s">
-        <v>160</v>
-      </c>
       <c r="M34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
@@ -2848,7 +2848,7 @@
         <v>12030</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2860,28 +2860,28 @@
         <v>39</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J35" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" t="s">
+        <v>42</v>
+      </c>
+      <c r="L35" t="s">
+        <v>47</v>
+      </c>
+      <c r="M35" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" t="s">
         <v>162</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35" t="s">
-        <v>42</v>
-      </c>
-      <c r="K35" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35" t="s">
-        <v>48</v>
-      </c>
-      <c r="M35" t="s">
-        <v>49</v>
-      </c>
-      <c r="N35" t="s">
-        <v>163</v>
-      </c>
       <c r="P35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
@@ -2889,46 +2889,46 @@
         <v>12031</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F36" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J36" t="s">
+        <v>46</v>
+      </c>
+      <c r="K36" t="s">
+        <v>42</v>
+      </c>
+      <c r="L36" t="s">
+        <v>47</v>
+      </c>
+      <c r="M36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N36" t="s">
         <v>165</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J36" t="s">
-        <v>47</v>
-      </c>
-      <c r="K36" t="s">
-        <v>43</v>
-      </c>
-      <c r="L36" t="s">
-        <v>48</v>
-      </c>
-      <c r="M36" t="s">
-        <v>49</v>
-      </c>
-      <c r="N36" t="s">
-        <v>166</v>
-      </c>
       <c r="P36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
@@ -2936,34 +2936,34 @@
         <v>12032</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J37" t="s">
+        <v>46</v>
+      </c>
+      <c r="K37" t="s">
+        <v>42</v>
+      </c>
+      <c r="L37" t="s">
         <v>168</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" t="s">
-        <v>47</v>
-      </c>
-      <c r="K37" t="s">
-        <v>43</v>
-      </c>
-      <c r="L37" t="s">
-        <v>169</v>
-      </c>
       <c r="M37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
@@ -2971,7 +2971,7 @@
         <v>12033</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -2983,28 +2983,28 @@
         <v>39</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
@@ -3012,7 +3012,7 @@
         <v>12034</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -3024,34 +3024,34 @@
         <v>39</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K39" t="s">
+        <v>42</v>
+      </c>
+      <c r="L39" t="s">
         <v>43</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>44</v>
       </c>
-      <c r="M39" t="s">
-        <v>45</v>
-      </c>
       <c r="N39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
@@ -3059,7 +3059,7 @@
         <v>12035</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -3068,25 +3068,25 @@
         <v>38</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
@@ -3094,7 +3094,7 @@
         <v>12036</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -3106,37 +3106,37 @@
         <v>39</v>
       </c>
       <c r="F41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J41" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" t="s">
+        <v>42</v>
+      </c>
+      <c r="L41" t="s">
+        <v>143</v>
+      </c>
+      <c r="M41" t="s">
+        <v>48</v>
+      </c>
+      <c r="N41" t="s">
+        <v>102</v>
+      </c>
+      <c r="P41" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" t="s">
         <v>177</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" t="s">
-        <v>144</v>
-      </c>
-      <c r="M41" t="s">
-        <v>49</v>
-      </c>
-      <c r="N41" t="s">
-        <v>103</v>
-      </c>
-      <c r="P41" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>178</v>
-      </c>
       <c r="R41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
@@ -3144,46 +3144,46 @@
         <v>12037</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J42" t="s">
+        <v>46</v>
+      </c>
+      <c r="K42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L42" t="s">
+        <v>47</v>
+      </c>
+      <c r="M42" t="s">
+        <v>48</v>
+      </c>
+      <c r="N42" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" t="s">
-        <v>43</v>
-      </c>
-      <c r="L42" t="s">
-        <v>48</v>
-      </c>
-      <c r="M42" t="s">
-        <v>49</v>
-      </c>
-      <c r="N42" t="s">
-        <v>181</v>
-      </c>
       <c r="P42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
@@ -3191,52 +3191,52 @@
         <v>12038</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F43" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K43" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" t="s">
+        <v>47</v>
+      </c>
+      <c r="M43" t="s">
+        <v>48</v>
+      </c>
+      <c r="N43" t="s">
         <v>183</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" t="s">
-        <v>47</v>
-      </c>
-      <c r="K43" t="s">
-        <v>43</v>
-      </c>
-      <c r="L43" t="s">
-        <v>48</v>
-      </c>
-      <c r="M43" t="s">
-        <v>49</v>
-      </c>
-      <c r="N43" t="s">
+      <c r="P43" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q43" t="s">
         <v>184</v>
       </c>
-      <c r="P43" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
+        <v>48</v>
+      </c>
+      <c r="S43" t="s">
+        <v>90</v>
+      </c>
+      <c r="U43" t="s">
         <v>185</v>
-      </c>
-      <c r="R43" t="s">
-        <v>49</v>
-      </c>
-      <c r="S43" t="s">
-        <v>91</v>
-      </c>
-      <c r="U43" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
@@ -3244,46 +3244,46 @@
         <v>12039</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F44" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J44" t="s">
+        <v>46</v>
+      </c>
+      <c r="K44" t="s">
+        <v>42</v>
+      </c>
+      <c r="L44" t="s">
+        <v>47</v>
+      </c>
+      <c r="M44" t="s">
+        <v>48</v>
+      </c>
+      <c r="N44" t="s">
         <v>188</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J44" t="s">
-        <v>47</v>
-      </c>
-      <c r="K44" t="s">
-        <v>43</v>
-      </c>
-      <c r="L44" t="s">
-        <v>48</v>
-      </c>
-      <c r="M44" t="s">
-        <v>49</v>
-      </c>
-      <c r="N44" t="s">
-        <v>189</v>
-      </c>
       <c r="P44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
@@ -3291,40 +3291,40 @@
         <v>12040</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J45" t="s">
+        <v>46</v>
+      </c>
+      <c r="K45" t="s">
+        <v>42</v>
+      </c>
+      <c r="L45" t="s">
         <v>191</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" t="s">
-        <v>43</v>
-      </c>
-      <c r="L45" t="s">
-        <v>192</v>
-      </c>
       <c r="M45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
@@ -3332,61 +3332,61 @@
         <v>12041</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E46" t="s">
         <v>39</v>
       </c>
       <c r="F46" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J46" t="s">
         <v>194</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J46" t="s">
-        <v>195</v>
-      </c>
       <c r="K46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
@@ -3394,49 +3394,49 @@
         <v>12042</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E47" t="s">
         <v>39</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U47" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
@@ -3444,58 +3444,58 @@
         <v>12043</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F48" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J48" t="s">
+        <v>46</v>
+      </c>
+      <c r="K48" t="s">
+        <v>42</v>
+      </c>
+      <c r="L48" t="s">
+        <v>47</v>
+      </c>
+      <c r="M48" t="s">
+        <v>48</v>
+      </c>
+      <c r="N48" t="s">
         <v>199</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J48" t="s">
-        <v>47</v>
-      </c>
-      <c r="K48" t="s">
-        <v>43</v>
-      </c>
-      <c r="L48" t="s">
-        <v>48</v>
-      </c>
-      <c r="M48" t="s">
-        <v>49</v>
-      </c>
-      <c r="N48" t="s">
-        <v>200</v>
-      </c>
       <c r="P48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
@@ -3503,43 +3503,43 @@
         <v>12044</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J49" t="s">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s">
+        <v>42</v>
+      </c>
+      <c r="L49" t="s">
         <v>202</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" t="s">
-        <v>75</v>
-      </c>
-      <c r="K49" t="s">
-        <v>43</v>
-      </c>
-      <c r="L49" t="s">
-        <v>203</v>
-      </c>
       <c r="M49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
@@ -3547,40 +3547,40 @@
         <v>12045</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E50" t="s">
         <v>39</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
@@ -3588,37 +3588,37 @@
         <v>12046</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E51" t="s">
         <v>39</v>
       </c>
       <c r="F51" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J51" t="s">
+        <v>46</v>
+      </c>
+      <c r="K51" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51" t="s">
         <v>207</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J51" t="s">
-        <v>47</v>
-      </c>
-      <c r="K51" t="s">
-        <v>43</v>
-      </c>
-      <c r="L51" t="s">
-        <v>208</v>
-      </c>
       <c r="M51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
@@ -3626,67 +3626,67 @@
         <v>12047</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F52" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J52" t="s">
+        <v>46</v>
+      </c>
+      <c r="K52" t="s">
+        <v>42</v>
+      </c>
+      <c r="L52" t="s">
+        <v>64</v>
+      </c>
+      <c r="M52" t="s">
+        <v>48</v>
+      </c>
+      <c r="P52" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" t="s">
         <v>210</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J52" t="s">
-        <v>47</v>
-      </c>
-      <c r="K52" t="s">
-        <v>43</v>
-      </c>
-      <c r="L52" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" t="s">
-        <v>49</v>
-      </c>
-      <c r="P52" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
+        <v>48</v>
+      </c>
+      <c r="S52" t="s">
         <v>211</v>
       </c>
-      <c r="R52" t="s">
-        <v>49</v>
-      </c>
-      <c r="S52" t="s">
+      <c r="T52" t="s">
+        <v>102</v>
+      </c>
+      <c r="U52" t="s">
+        <v>46</v>
+      </c>
+      <c r="V52" t="s">
+        <v>210</v>
+      </c>
+      <c r="W52" t="s">
+        <v>48</v>
+      </c>
+      <c r="X52" t="s">
         <v>212</v>
       </c>
-      <c r="T52" t="s">
-        <v>103</v>
-      </c>
-      <c r="U52" t="s">
-        <v>47</v>
-      </c>
-      <c r="V52" t="s">
-        <v>211</v>
-      </c>
-      <c r="W52" t="s">
-        <v>49</v>
-      </c>
-      <c r="X52" t="s">
-        <v>213</v>
-      </c>
       <c r="Y52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
@@ -3694,49 +3694,49 @@
         <v>12048</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E53" t="s">
         <v>39</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L53" t="s">
+        <v>64</v>
+      </c>
+      <c r="M53" t="s">
+        <v>48</v>
+      </c>
+      <c r="P53" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q53" t="s">
         <v>65</v>
       </c>
-      <c r="M53" t="s">
-        <v>49</v>
-      </c>
-      <c r="P53" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q53" t="s">
+      <c r="R53" t="s">
+        <v>48</v>
+      </c>
+      <c r="S53" t="s">
+        <v>56</v>
+      </c>
+      <c r="U53" t="s">
         <v>66</v>
-      </c>
-      <c r="R53" t="s">
-        <v>49</v>
-      </c>
-      <c r="S53" t="s">
-        <v>57</v>
-      </c>
-      <c r="U53" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
@@ -3744,64 +3744,64 @@
         <v>12049</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
@@ -3809,43 +3809,43 @@
         <v>12050</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E55" t="s">
         <v>39</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J55" t="s">
+        <v>46</v>
+      </c>
+      <c r="K55" t="s">
+        <v>42</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="M55" t="s">
+        <v>48</v>
+      </c>
+      <c r="N55" t="s">
+        <v>42</v>
+      </c>
+      <c r="O55" t="s">
         <v>219</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J55" t="s">
-        <v>47</v>
-      </c>
-      <c r="K55" t="s">
-        <v>43</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="M55" t="s">
-        <v>49</v>
-      </c>
-      <c r="N55" t="s">
-        <v>43</v>
-      </c>
-      <c r="O55" t="s">
-        <v>220</v>
-      </c>
       <c r="P55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
@@ -3853,46 +3853,46 @@
         <v>12051</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F56" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J56" t="s">
+        <v>46</v>
+      </c>
+      <c r="K56" t="s">
+        <v>42</v>
+      </c>
+      <c r="L56" t="s">
+        <v>47</v>
+      </c>
+      <c r="M56" t="s">
+        <v>48</v>
+      </c>
+      <c r="N56" t="s">
         <v>222</v>
       </c>
-      <c r="G56" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J56" t="s">
-        <v>47</v>
-      </c>
-      <c r="K56" t="s">
-        <v>43</v>
-      </c>
-      <c r="L56" t="s">
-        <v>48</v>
-      </c>
-      <c r="M56" t="s">
-        <v>49</v>
-      </c>
-      <c r="N56" t="s">
-        <v>223</v>
-      </c>
       <c r="P56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
@@ -3900,40 +3900,40 @@
         <v>12052</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F57" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J57" t="s">
+        <v>46</v>
+      </c>
+      <c r="K57" t="s">
+        <v>42</v>
+      </c>
+      <c r="L57" t="s">
         <v>225</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J57" t="s">
-        <v>47</v>
-      </c>
-      <c r="K57" t="s">
-        <v>43</v>
-      </c>
-      <c r="L57" t="s">
-        <v>226</v>
-      </c>
       <c r="M57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
@@ -3941,49 +3941,49 @@
         <v>12053</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E58" t="s">
         <v>39</v>
       </c>
       <c r="F58" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J58" t="s">
+        <v>46</v>
+      </c>
+      <c r="K58" t="s">
+        <v>42</v>
+      </c>
+      <c r="L58" t="s">
+        <v>64</v>
+      </c>
+      <c r="M58" t="s">
+        <v>48</v>
+      </c>
+      <c r="P58" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>43</v>
+      </c>
+      <c r="R58" t="s">
         <v>228</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J58" t="s">
-        <v>47</v>
-      </c>
-      <c r="K58" t="s">
-        <v>43</v>
-      </c>
-      <c r="L58" t="s">
-        <v>65</v>
-      </c>
-      <c r="M58" t="s">
-        <v>49</v>
-      </c>
-      <c r="P58" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>44</v>
-      </c>
-      <c r="R58" t="s">
-        <v>229</v>
-      </c>
       <c r="S58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
@@ -3991,43 +3991,43 @@
         <v>12054</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F59" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J59" t="s">
+        <v>46</v>
+      </c>
+      <c r="K59" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59" t="s">
+        <v>64</v>
+      </c>
+      <c r="M59" t="s">
+        <v>48</v>
+      </c>
+      <c r="P59" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" t="s">
         <v>231</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J59" t="s">
-        <v>47</v>
-      </c>
-      <c r="K59" t="s">
-        <v>43</v>
-      </c>
-      <c r="L59" t="s">
-        <v>65</v>
-      </c>
-      <c r="M59" t="s">
-        <v>49</v>
-      </c>
-      <c r="P59" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>232</v>
-      </c>
       <c r="R59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
@@ -4035,61 +4035,61 @@
         <v>12055</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
         <v>39</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="J60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q60" t="s">
+        <v>55</v>
+      </c>
+      <c r="R60" t="s">
+        <v>48</v>
+      </c>
+      <c r="S60" t="s">
         <v>56</v>
       </c>
-      <c r="R60" t="s">
-        <v>49</v>
-      </c>
-      <c r="S60" t="s">
-        <v>57</v>
-      </c>
       <c r="U60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="W60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
@@ -4097,49 +4097,49 @@
         <v>12056</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E61" t="s">
         <v>39</v>
       </c>
       <c r="F61" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="J61" t="s">
+        <v>194</v>
+      </c>
+      <c r="K61" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61" t="s">
+        <v>194</v>
+      </c>
+      <c r="M61" t="s">
+        <v>48</v>
+      </c>
+      <c r="P61" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q61" t="s">
         <v>236</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J61" t="s">
-        <v>195</v>
-      </c>
-      <c r="K61" t="s">
-        <v>43</v>
-      </c>
-      <c r="L61" t="s">
-        <v>195</v>
-      </c>
-      <c r="M61" t="s">
-        <v>49</v>
-      </c>
-      <c r="P61" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>237</v>
-      </c>
       <c r="R61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
